--- a/04_Figures/F04/c_data/F04_supplementary.xlsx
+++ b/04_Figures/F04/c_data/F04_supplementary.xlsx
@@ -41574,25 +41574,25 @@
         <v>257</v>
       </c>
       <c r="D2" t="n">
-        <v>3.48412721247144</v>
+        <v>3.48412721247087</v>
       </c>
       <c r="E2" t="n">
-        <v>4.21161096897943</v>
+        <v>4.21161096897874</v>
       </c>
       <c r="F2" t="n">
-        <v>0.511141040596112</v>
+        <v>0.511141040596108</v>
       </c>
       <c r="G2" t="n">
-        <v>0.556196949731643</v>
+        <v>0.556196949731639</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0287632004854426</v>
+        <v>0.0287632004854827</v>
       </c>
       <c r="I2" t="s">
         <v>258</v>
       </c>
       <c r="J2" t="n">
-        <v>4.21161096897943</v>
+        <v>4.21161096897874</v>
       </c>
       <c r="K2" t="s">
         <v>53</v>
@@ -41609,25 +41609,25 @@
         <v>257</v>
       </c>
       <c r="D3" t="n">
-        <v>4.05790561093459</v>
+        <v>4.0579056109332</v>
       </c>
       <c r="E3" t="n">
-        <v>4.09186896159811</v>
+        <v>4.09186896159673</v>
       </c>
       <c r="F3" t="n">
         <v>0.706915668807515</v>
       </c>
       <c r="G3" t="n">
-        <v>0.647715157272707</v>
+        <v>0.64771515727271</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0021342337189146</v>
+        <v>0.00213423371892398</v>
       </c>
       <c r="I3" t="s">
         <v>258</v>
       </c>
       <c r="J3" t="n">
-        <v>4.09186896159811</v>
+        <v>4.09186896159673</v>
       </c>
       <c r="K3" t="s">
         <v>53</v>
@@ -41644,25 +41644,25 @@
         <v>259</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.48817220034395</v>
+        <v>-3.48817220034216</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.45429041055526</v>
+        <v>-3.45429041055345</v>
       </c>
       <c r="F4" t="n">
         <v>-0.764142564725145</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.739464072659473</v>
+        <v>-0.739464072659466</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00480638078838086</v>
+        <v>0.00480638078840438</v>
       </c>
       <c r="I4" t="s">
         <v>260</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45429041055526</v>
+        <v>3.45429041055345</v>
       </c>
       <c r="K4" t="s">
         <v>77</v>
@@ -41679,10 +41679,10 @@
         <v>257</v>
       </c>
       <c r="D5" t="n">
-        <v>2.59704840828352</v>
+        <v>2.59704840828154</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4307237061489</v>
+        <v>3.43072370614627</v>
       </c>
       <c r="F5" t="n">
         <v>1.10652955402938</v>
@@ -41691,13 +41691,13 @@
         <v>1.71883830144357</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00758883678458743</v>
+        <v>0.00758883678463336</v>
       </c>
       <c r="I5" t="s">
         <v>258</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4307237061489</v>
+        <v>3.43072370614627</v>
       </c>
       <c r="K5" t="s">
         <v>53</v>
@@ -41714,25 +41714,25 @@
         <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.64310062264202</v>
+        <v>-4.6431006226428</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.91801758322947</v>
+        <v>-2.91801758322992</v>
       </c>
       <c r="F6" t="n">
         <v>-0.481424194198407</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.309755822129897</v>
+        <v>-0.309755822129894</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00523848038285882</v>
+        <v>0.00523848038285669</v>
       </c>
       <c r="I6" t="s">
         <v>260</v>
       </c>
       <c r="J6" t="n">
-        <v>2.91801758322947</v>
+        <v>2.91801758322992</v>
       </c>
       <c r="K6" t="s">
         <v>77</v>
@@ -41749,25 +41749,25 @@
         <v>257</v>
       </c>
       <c r="D7" t="n">
-        <v>3.76368067195969</v>
+        <v>3.7636806719603</v>
       </c>
       <c r="E7" t="n">
-        <v>2.88994882485847</v>
+        <v>2.88994882485898</v>
       </c>
       <c r="F7" t="n">
         <v>0.390491085452169</v>
       </c>
       <c r="G7" t="n">
-        <v>0.306973060642736</v>
+        <v>0.30697306064274</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0458883291390347</v>
+        <v>0.0458883291390167</v>
       </c>
       <c r="I7" t="s">
         <v>258</v>
       </c>
       <c r="J7" t="n">
-        <v>2.88994882485847</v>
+        <v>2.88994882485898</v>
       </c>
       <c r="K7" t="s">
         <v>53</v>
@@ -41784,25 +41784,25 @@
         <v>257</v>
       </c>
       <c r="D8" t="n">
-        <v>4.63625010648219</v>
+        <v>4.63625010648508</v>
       </c>
       <c r="E8" t="n">
-        <v>2.88766399959163</v>
+        <v>2.88766399959336</v>
       </c>
       <c r="F8" t="n">
-        <v>0.433831594366467</v>
+        <v>0.43383159436647</v>
       </c>
       <c r="G8" t="n">
-        <v>0.25369598668917</v>
+        <v>0.253695986689166</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00936752333387038</v>
+        <v>0.00936752333383787</v>
       </c>
       <c r="I8" t="s">
         <v>258</v>
       </c>
       <c r="J8" t="n">
-        <v>2.88766399959163</v>
+        <v>2.88766399959336</v>
       </c>
       <c r="K8" t="s">
         <v>53</v>
@@ -41819,25 +41819,25 @@
         <v>257</v>
       </c>
       <c r="D9" t="n">
-        <v>5.39120431822511</v>
+        <v>5.39120431822785</v>
       </c>
       <c r="E9" t="n">
-        <v>2.75946428310905</v>
+        <v>2.75946428311049</v>
       </c>
       <c r="F9" t="n">
         <v>0.473425956401499</v>
       </c>
       <c r="G9" t="n">
-        <v>0.248086314903819</v>
+        <v>0.248086314903823</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00154451475019756</v>
+        <v>0.00154451475019221</v>
       </c>
       <c r="I9" t="s">
         <v>258</v>
       </c>
       <c r="J9" t="n">
-        <v>2.75946428310905</v>
+        <v>2.75946428311049</v>
       </c>
       <c r="K9" t="s">
         <v>53</v>
@@ -41854,25 +41854,25 @@
         <v>259</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2056473247244</v>
+        <v>-3.2056473247226</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.70712786773506</v>
+        <v>-2.70712786773349</v>
       </c>
       <c r="F10" t="n">
         <v>-0.814653105627791</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.693627278270903</v>
+        <v>-0.693627278270892</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00669950361201134</v>
+        <v>0.0066995036120439</v>
       </c>
       <c r="I10" t="s">
         <v>260</v>
       </c>
       <c r="J10" t="n">
-        <v>2.70712786773506</v>
+        <v>2.70712786773349</v>
       </c>
       <c r="K10" t="s">
         <v>77</v>
@@ -41889,10 +41889,10 @@
         <v>257</v>
       </c>
       <c r="D11" t="n">
-        <v>4.62111071584486</v>
+        <v>4.62111071584234</v>
       </c>
       <c r="E11" t="n">
-        <v>2.67928195405195</v>
+        <v>2.67928195405049</v>
       </c>
       <c r="F11" t="n">
         <v>1.11357792651978</v>
@@ -41901,13 +41901,13 @@
         <v>0.661004499617025</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00000578698121708469</v>
+        <v>0.00000578698121715527</v>
       </c>
       <c r="I11" t="s">
         <v>258</v>
       </c>
       <c r="J11" t="n">
-        <v>2.67928195405195</v>
+        <v>2.67928195405049</v>
       </c>
       <c r="K11" t="s">
         <v>53</v>
@@ -41924,10 +41924,10 @@
         <v>259</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.91392784946546</v>
+        <v>-2.91392784946407</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.46744007168066</v>
+        <v>-2.46744007167948</v>
       </c>
       <c r="F12" t="n">
         <v>-0.608293578130187</v>
@@ -41936,13 +41936,13 @@
         <v>-0.441667173414015</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0423994348400066</v>
+        <v>0.0423994348401228</v>
       </c>
       <c r="I12" t="s">
         <v>260</v>
       </c>
       <c r="J12" t="n">
-        <v>2.46744007168066</v>
+        <v>2.46744007167948</v>
       </c>
       <c r="K12" t="s">
         <v>77</v>
@@ -41959,10 +41959,10 @@
         <v>257</v>
       </c>
       <c r="D13" t="n">
-        <v>3.56494917113652</v>
+        <v>3.56494917113547</v>
       </c>
       <c r="E13" t="n">
-        <v>2.43367358253559</v>
+        <v>2.43367358253488</v>
       </c>
       <c r="F13" t="n">
         <v>0.538929847075671</v>
@@ -41971,13 +41971,13 @@
         <v>0.376663015654117</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0200502138750866</v>
+        <v>0.0200502138751314</v>
       </c>
       <c r="I13" t="s">
         <v>258</v>
       </c>
       <c r="J13" t="n">
-        <v>2.43367358253559</v>
+        <v>2.43367358253488</v>
       </c>
       <c r="K13" t="s">
         <v>53</v>
@@ -41994,25 +41994,25 @@
         <v>259</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.18249954175652</v>
+        <v>-4.18249954175475</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.37026507714477</v>
+        <v>-2.37026507714375</v>
       </c>
       <c r="F14" t="n">
         <v>-0.769667406399485</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.431402455948795</v>
+        <v>-0.431402455948792</v>
       </c>
       <c r="H14" t="n">
-        <v>0.000803919817790013</v>
+        <v>0.000803919817794644</v>
       </c>
       <c r="I14" t="s">
         <v>260</v>
       </c>
       <c r="J14" t="n">
-        <v>2.37026507714477</v>
+        <v>2.37026507714375</v>
       </c>
       <c r="K14" t="s">
         <v>77</v>
@@ -42029,25 +42029,25 @@
         <v>257</v>
       </c>
       <c r="D15" t="n">
-        <v>3.25356019722984</v>
+        <v>3.25356019722794</v>
       </c>
       <c r="E15" t="n">
-        <v>2.32286999909673</v>
+        <v>2.32286999909538</v>
       </c>
       <c r="F15" t="n">
         <v>0.900404254930402</v>
       </c>
       <c r="G15" t="n">
-        <v>0.413709003406984</v>
+        <v>0.413709003406986</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00466372750745126</v>
+        <v>0.00466372750748004</v>
       </c>
       <c r="I15" t="s">
         <v>258</v>
       </c>
       <c r="J15" t="n">
-        <v>2.32286999909673</v>
+        <v>2.32286999909538</v>
       </c>
       <c r="K15" t="s">
         <v>53</v>
@@ -42064,25 +42064,25 @@
         <v>257</v>
       </c>
       <c r="D16" t="n">
-        <v>4.01785730469738</v>
+        <v>4.01785730469829</v>
       </c>
       <c r="E16" t="n">
-        <v>2.29300875076177</v>
+        <v>2.29300875076236</v>
       </c>
       <c r="F16" t="n">
         <v>0.402624473620964</v>
       </c>
       <c r="G16" t="n">
-        <v>0.235246478227097</v>
+        <v>0.235246478227104</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0297225836246326</v>
+        <v>0.0297225836246106</v>
       </c>
       <c r="I16" t="s">
         <v>258</v>
       </c>
       <c r="J16" t="n">
-        <v>2.29300875076177</v>
+        <v>2.29300875076236</v>
       </c>
       <c r="K16" t="s">
         <v>53</v>
@@ -42099,25 +42099,25 @@
         <v>257</v>
       </c>
       <c r="D17" t="n">
-        <v>3.98464356645327</v>
+        <v>3.98464356645527</v>
       </c>
       <c r="E17" t="n">
-        <v>2.258562043822</v>
+        <v>2.25856204382324</v>
       </c>
       <c r="F17" t="n">
-        <v>0.349460320731538</v>
+        <v>0.349460320731534</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2027926331901</v>
+        <v>0.202792633190107</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0491609257512685</v>
+        <v>0.0491609257511754</v>
       </c>
       <c r="I17" t="s">
         <v>258</v>
       </c>
       <c r="J17" t="n">
-        <v>2.258562043822</v>
+        <v>2.25856204382324</v>
       </c>
       <c r="K17" t="s">
         <v>53</v>
@@ -42134,10 +42134,10 @@
         <v>257</v>
       </c>
       <c r="D18" t="n">
-        <v>3.73354463132608</v>
+        <v>3.73354463132412</v>
       </c>
       <c r="E18" t="n">
-        <v>2.13914502585512</v>
+        <v>2.139145025854</v>
       </c>
       <c r="F18" t="n">
         <v>0.776205944356491</v>
@@ -42146,13 +42146,13 @@
         <v>0.452181538535665</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00257723117456075</v>
+        <v>0.00257723117457561</v>
       </c>
       <c r="I18" t="s">
         <v>258</v>
       </c>
       <c r="J18" t="n">
-        <v>2.13914502585512</v>
+        <v>2.139145025854</v>
       </c>
       <c r="K18" t="s">
         <v>53</v>
@@ -42169,10 +42169,10 @@
         <v>257</v>
       </c>
       <c r="D19" t="n">
-        <v>3.90789142328878</v>
+        <v>3.90789142328785</v>
       </c>
       <c r="E19" t="n">
-        <v>2.02585547110816</v>
+        <v>2.02585547110767</v>
       </c>
       <c r="F19" t="n">
         <v>0.611262057913592</v>
@@ -42181,13 +42181,13 @@
         <v>0.285039023149753</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00639334703822229</v>
+        <v>0.00639334703823942</v>
       </c>
       <c r="I19" t="s">
         <v>258</v>
       </c>
       <c r="J19" t="n">
-        <v>2.02585547110816</v>
+        <v>2.02585547110767</v>
       </c>
       <c r="K19" t="s">
         <v>53</v>
@@ -42204,25 +42204,25 @@
         <v>257</v>
       </c>
       <c r="D20" t="n">
-        <v>4.63999909161891</v>
+        <v>4.63999909161652</v>
       </c>
       <c r="E20" t="n">
-        <v>1.95027028471477</v>
+        <v>1.95027028471379</v>
       </c>
       <c r="F20" t="n">
         <v>1.01770635395491</v>
       </c>
       <c r="G20" t="n">
-        <v>0.437936508011408</v>
+        <v>0.437936508011411</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0000152558240329483</v>
+        <v>0.000015255824033112</v>
       </c>
       <c r="I20" t="s">
         <v>258</v>
       </c>
       <c r="J20" t="n">
-        <v>1.95027028471477</v>
+        <v>1.95027028471379</v>
       </c>
       <c r="K20" t="s">
         <v>53</v>
@@ -42239,10 +42239,10 @@
         <v>257</v>
       </c>
       <c r="D21" t="n">
-        <v>4.98144460589364</v>
+        <v>4.98144460589408</v>
       </c>
       <c r="E21" t="n">
-        <v>1.94065606360787</v>
+        <v>1.94065606360804</v>
       </c>
       <c r="F21" t="n">
         <v>0.540644965102562</v>
@@ -42251,13 +42251,13 @@
         <v>0.215633974661486</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0014107092744133</v>
+        <v>0.0014107092744139</v>
       </c>
       <c r="I21" t="s">
         <v>258</v>
       </c>
       <c r="J21" t="n">
-        <v>1.94065606360787</v>
+        <v>1.94065606360804</v>
       </c>
       <c r="K21" t="s">
         <v>53</v>

--- a/04_Figures/F04/c_data/F04_supplementary.xlsx
+++ b/04_Figures/F04/c_data/F04_supplementary.xlsx
@@ -19742,7 +19742,7 @@
         <v>1703</v>
       </c>
       <c r="J2" t="n">
-        <v>2.41844683469722</v>
+        <v>2.41844683469761</v>
       </c>
       <c r="K2" t="s">
         <v>1704</v>
@@ -19777,7 +19777,7 @@
         <v>1703</v>
       </c>
       <c r="J3" t="n">
-        <v>2.41844683469722</v>
+        <v>2.41844683469761</v>
       </c>
       <c r="K3" t="s">
         <v>1706</v>
@@ -19812,7 +19812,7 @@
         <v>1703</v>
       </c>
       <c r="J4" t="n">
-        <v>2.41844683469722</v>
+        <v>2.41844683469761</v>
       </c>
       <c r="K4" t="s">
         <v>1708</v>
@@ -19847,7 +19847,7 @@
         <v>1703</v>
       </c>
       <c r="J5" t="n">
-        <v>2.24517099861892</v>
+        <v>2.24517099861893</v>
       </c>
       <c r="K5" t="s">
         <v>1709</v>
@@ -19882,7 +19882,7 @@
         <v>1703</v>
       </c>
       <c r="J6" t="n">
-        <v>2.24517099861892</v>
+        <v>2.24517099861893</v>
       </c>
       <c r="K6" t="s">
         <v>1710</v>
@@ -19917,7 +19917,7 @@
         <v>1703</v>
       </c>
       <c r="J7" t="n">
-        <v>2.24517099861892</v>
+        <v>2.24517099861893</v>
       </c>
       <c r="K7" t="s">
         <v>1711</v>
@@ -19952,7 +19952,7 @@
         <v>1703</v>
       </c>
       <c r="J8" t="n">
-        <v>2.19635206365832</v>
+        <v>2.1963520636585</v>
       </c>
       <c r="K8" t="s">
         <v>1712</v>
@@ -19987,7 +19987,7 @@
         <v>1703</v>
       </c>
       <c r="J9" t="n">
-        <v>2.19635206365832</v>
+        <v>2.1963520636585</v>
       </c>
       <c r="K9" t="s">
         <v>1713</v>
@@ -20022,7 +20022,7 @@
         <v>1703</v>
       </c>
       <c r="J10" t="n">
-        <v>2.19635206365832</v>
+        <v>2.1963520636585</v>
       </c>
       <c r="K10" t="s">
         <v>1714</v>
@@ -20057,7 +20057,7 @@
         <v>1703</v>
       </c>
       <c r="J11" t="n">
-        <v>1.94415529758707</v>
+        <v>1.94415529758733</v>
       </c>
       <c r="K11" t="s">
         <v>1715</v>
@@ -20092,7 +20092,7 @@
         <v>1703</v>
       </c>
       <c r="J12" t="n">
-        <v>1.94415529758707</v>
+        <v>1.94415529758733</v>
       </c>
       <c r="K12" t="s">
         <v>1716</v>
@@ -20127,7 +20127,7 @@
         <v>1703</v>
       </c>
       <c r="J13" t="n">
-        <v>1.94415529758707</v>
+        <v>1.94415529758733</v>
       </c>
       <c r="K13" t="s">
         <v>1717</v>
@@ -20162,7 +20162,7 @@
         <v>1703</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9038387056987</v>
+        <v>1.90383870569905</v>
       </c>
       <c r="K14" t="s">
         <v>1718</v>
@@ -20197,7 +20197,7 @@
         <v>1703</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9038387056987</v>
+        <v>1.90383870569905</v>
       </c>
       <c r="K15" t="s">
         <v>1719</v>
@@ -20232,7 +20232,7 @@
         <v>1703</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9038387056987</v>
+        <v>1.90383870569905</v>
       </c>
       <c r="K16" t="s">
         <v>1720</v>
@@ -20267,7 +20267,7 @@
         <v>1703</v>
       </c>
       <c r="J17" t="n">
-        <v>1.87386365247344</v>
+        <v>1.87386365247357</v>
       </c>
       <c r="K17" t="s">
         <v>1721</v>
@@ -20302,7 +20302,7 @@
         <v>1703</v>
       </c>
       <c r="J18" t="n">
-        <v>1.87386365247344</v>
+        <v>1.87386365247357</v>
       </c>
       <c r="K18" t="s">
         <v>1722</v>
@@ -20337,7 +20337,7 @@
         <v>1703</v>
       </c>
       <c r="J19" t="n">
-        <v>1.87386365247344</v>
+        <v>1.87386365247357</v>
       </c>
       <c r="K19" t="s">
         <v>1723</v>
@@ -20372,7 +20372,7 @@
         <v>1703</v>
       </c>
       <c r="J20" t="n">
-        <v>1.73574654835547</v>
+        <v>1.73574654835555</v>
       </c>
       <c r="K20" t="s">
         <v>1724</v>
@@ -20407,7 +20407,7 @@
         <v>1703</v>
       </c>
       <c r="J21" t="n">
-        <v>1.73574654835547</v>
+        <v>1.73574654835555</v>
       </c>
       <c r="K21" t="s">
         <v>1725</v>
@@ -20442,7 +20442,7 @@
         <v>1703</v>
       </c>
       <c r="J22" t="n">
-        <v>1.73574654835547</v>
+        <v>1.73574654835555</v>
       </c>
       <c r="K22" t="s">
         <v>1726</v>
@@ -20477,7 +20477,7 @@
         <v>1703</v>
       </c>
       <c r="J23" t="n">
-        <v>1.70740921447616</v>
+        <v>1.70740921447641</v>
       </c>
       <c r="K23" t="s">
         <v>1727</v>
@@ -20512,7 +20512,7 @@
         <v>1703</v>
       </c>
       <c r="J24" t="n">
-        <v>1.70740921447616</v>
+        <v>1.70740921447641</v>
       </c>
       <c r="K24" t="s">
         <v>1728</v>
@@ -20547,7 +20547,7 @@
         <v>1703</v>
       </c>
       <c r="J25" t="n">
-        <v>1.70740921447616</v>
+        <v>1.70740921447641</v>
       </c>
       <c r="K25" t="s">
         <v>1729</v>
@@ -20582,7 +20582,7 @@
         <v>1730</v>
       </c>
       <c r="J26" t="n">
-        <v>2.64428916077595</v>
+        <v>2.64428916077651</v>
       </c>
       <c r="K26" t="s">
         <v>1731</v>
@@ -20617,7 +20617,7 @@
         <v>1730</v>
       </c>
       <c r="J27" t="n">
-        <v>2.64428916077595</v>
+        <v>2.64428916077651</v>
       </c>
       <c r="K27" t="s">
         <v>1732</v>
@@ -20652,7 +20652,7 @@
         <v>1730</v>
       </c>
       <c r="J28" t="n">
-        <v>2.64428916077595</v>
+        <v>2.64428916077651</v>
       </c>
       <c r="K28" t="s">
         <v>1733</v>
@@ -20687,7 +20687,7 @@
         <v>1730</v>
       </c>
       <c r="J29" t="n">
-        <v>2.44654564939067</v>
+        <v>2.44654564939118</v>
       </c>
       <c r="K29" t="s">
         <v>1734</v>
@@ -20722,7 +20722,7 @@
         <v>1730</v>
       </c>
       <c r="J30" t="n">
-        <v>2.44654564939067</v>
+        <v>2.44654564939118</v>
       </c>
       <c r="K30" t="s">
         <v>1735</v>
@@ -20757,7 +20757,7 @@
         <v>1730</v>
       </c>
       <c r="J31" t="n">
-        <v>2.44654564939067</v>
+        <v>2.44654564939118</v>
       </c>
       <c r="K31" t="s">
         <v>1736</v>
@@ -20792,7 +20792,7 @@
         <v>1730</v>
       </c>
       <c r="J32" t="n">
-        <v>2.43481842735811</v>
+        <v>2.43481842735863</v>
       </c>
       <c r="K32" t="s">
         <v>1737</v>
@@ -20827,7 +20827,7 @@
         <v>1730</v>
       </c>
       <c r="J33" t="n">
-        <v>2.43481842735811</v>
+        <v>2.43481842735863</v>
       </c>
       <c r="K33" t="s">
         <v>1738</v>
@@ -20862,7 +20862,7 @@
         <v>1730</v>
       </c>
       <c r="J34" t="n">
-        <v>2.43481842735811</v>
+        <v>2.43481842735863</v>
       </c>
       <c r="K34" t="s">
         <v>1739</v>
@@ -20897,7 +20897,7 @@
         <v>1730</v>
       </c>
       <c r="J35" t="n">
-        <v>2.41909587394015</v>
+        <v>2.41909587394054</v>
       </c>
       <c r="K35" t="s">
         <v>1740</v>
@@ -20932,7 +20932,7 @@
         <v>1730</v>
       </c>
       <c r="J36" t="n">
-        <v>2.41909587394015</v>
+        <v>2.41909587394054</v>
       </c>
       <c r="K36" t="s">
         <v>1741</v>
@@ -20967,7 +20967,7 @@
         <v>1730</v>
       </c>
       <c r="J37" t="n">
-        <v>2.41909587394015</v>
+        <v>2.41909587394054</v>
       </c>
       <c r="K37" t="s">
         <v>1742</v>
@@ -21002,7 +21002,7 @@
         <v>1730</v>
       </c>
       <c r="J38" t="n">
-        <v>2.36980250578002</v>
+        <v>2.36980250578033</v>
       </c>
       <c r="K38" t="s">
         <v>1743</v>
@@ -21037,7 +21037,7 @@
         <v>1730</v>
       </c>
       <c r="J39" t="n">
-        <v>2.36980250578002</v>
+        <v>2.36980250578033</v>
       </c>
       <c r="K39" t="s">
         <v>1744</v>
@@ -21072,7 +21072,7 @@
         <v>1730</v>
       </c>
       <c r="J40" t="n">
-        <v>2.36980250578002</v>
+        <v>2.36980250578033</v>
       </c>
       <c r="K40" t="s">
         <v>1745</v>
@@ -21107,7 +21107,7 @@
         <v>1730</v>
       </c>
       <c r="J41" t="n">
-        <v>2.35994803598027</v>
+        <v>2.35994803598074</v>
       </c>
       <c r="K41" t="s">
         <v>1748</v>
@@ -21142,7 +21142,7 @@
         <v>1730</v>
       </c>
       <c r="J42" t="n">
-        <v>2.35994803598027</v>
+        <v>2.35994803598074</v>
       </c>
       <c r="K42" t="s">
         <v>1749</v>
@@ -21177,7 +21177,7 @@
         <v>1730</v>
       </c>
       <c r="J43" t="n">
-        <v>2.35994803598027</v>
+        <v>2.35994803598074</v>
       </c>
       <c r="K43" t="s">
         <v>1750</v>
@@ -21212,7 +21212,7 @@
         <v>1730</v>
       </c>
       <c r="J44" t="n">
-        <v>2.34507779862229</v>
+        <v>2.3450777986227</v>
       </c>
       <c r="K44" t="s">
         <v>1751</v>
@@ -21247,7 +21247,7 @@
         <v>1730</v>
       </c>
       <c r="J45" t="n">
-        <v>2.34507779862229</v>
+        <v>2.3450777986227</v>
       </c>
       <c r="K45" t="s">
         <v>1752</v>
@@ -21282,7 +21282,7 @@
         <v>1730</v>
       </c>
       <c r="J46" t="n">
-        <v>2.34507779862229</v>
+        <v>2.3450777986227</v>
       </c>
       <c r="K46" t="s">
         <v>1753</v>
@@ -21317,7 +21317,7 @@
         <v>1730</v>
       </c>
       <c r="J47" t="n">
-        <v>2.26140020194602</v>
+        <v>2.26140020194645</v>
       </c>
       <c r="K47" t="s">
         <v>1754</v>
@@ -21352,7 +21352,7 @@
         <v>1730</v>
       </c>
       <c r="J48" t="n">
-        <v>2.26140020194602</v>
+        <v>2.26140020194645</v>
       </c>
       <c r="K48" t="s">
         <v>1755</v>
@@ -21387,7 +21387,7 @@
         <v>1730</v>
       </c>
       <c r="J49" t="n">
-        <v>2.26140020194602</v>
+        <v>2.26140020194645</v>
       </c>
       <c r="K49" t="s">
         <v>1756</v>
@@ -21422,7 +21422,7 @@
         <v>1730</v>
       </c>
       <c r="J50" t="n">
-        <v>2.24498982775335</v>
+        <v>2.24498982775365</v>
       </c>
       <c r="K50" t="s">
         <v>1757</v>
@@ -21457,7 +21457,7 @@
         <v>1730</v>
       </c>
       <c r="J51" t="n">
-        <v>2.24498982775335</v>
+        <v>2.24498982775365</v>
       </c>
       <c r="K51" t="s">
         <v>1758</v>
@@ -21492,7 +21492,7 @@
         <v>1730</v>
       </c>
       <c r="J52" t="n">
-        <v>2.24498982775335</v>
+        <v>2.24498982775365</v>
       </c>
       <c r="K52" t="s">
         <v>1759</v>
@@ -21527,7 +21527,7 @@
         <v>1730</v>
       </c>
       <c r="J53" t="n">
-        <v>2.18221967326727</v>
+        <v>2.18221967326757</v>
       </c>
       <c r="K53" t="s">
         <v>1762</v>
@@ -21562,7 +21562,7 @@
         <v>1730</v>
       </c>
       <c r="J54" t="n">
-        <v>2.18221967326727</v>
+        <v>2.18221967326757</v>
       </c>
       <c r="K54" t="s">
         <v>1763</v>
@@ -21597,7 +21597,7 @@
         <v>1730</v>
       </c>
       <c r="J55" t="n">
-        <v>2.18221967326727</v>
+        <v>2.18221967326757</v>
       </c>
       <c r="K55" t="s">
         <v>1764</v>
@@ -21632,7 +21632,7 @@
         <v>1730</v>
       </c>
       <c r="J56" t="n">
-        <v>2.15239690834466</v>
+        <v>2.15239690834462</v>
       </c>
       <c r="K56" t="s">
         <v>1767</v>
@@ -21667,7 +21667,7 @@
         <v>1730</v>
       </c>
       <c r="J57" t="n">
-        <v>2.15239690834466</v>
+        <v>2.15239690834462</v>
       </c>
       <c r="K57" t="s">
         <v>1768</v>
@@ -21702,7 +21702,7 @@
         <v>1730</v>
       </c>
       <c r="J58" t="n">
-        <v>2.15239690834466</v>
+        <v>2.15239690834462</v>
       </c>
       <c r="K58" t="s">
         <v>1769</v>
@@ -21737,7 +21737,7 @@
         <v>1730</v>
       </c>
       <c r="J59" t="n">
-        <v>2.11835084340534</v>
+        <v>2.11835084340555</v>
       </c>
       <c r="K59" t="s">
         <v>1772</v>
@@ -21772,7 +21772,7 @@
         <v>1730</v>
       </c>
       <c r="J60" t="n">
-        <v>2.11835084340534</v>
+        <v>2.11835084340555</v>
       </c>
       <c r="K60" t="s">
         <v>1773</v>
@@ -21807,7 +21807,7 @@
         <v>1730</v>
       </c>
       <c r="J61" t="n">
-        <v>2.11835084340534</v>
+        <v>2.11835084340555</v>
       </c>
       <c r="K61" t="s">
         <v>1774</v>
@@ -21842,7 +21842,7 @@
         <v>1730</v>
       </c>
       <c r="J62" t="n">
-        <v>2.0915690933872</v>
+        <v>2.09156909338722</v>
       </c>
       <c r="K62" t="s">
         <v>1777</v>
@@ -21877,7 +21877,7 @@
         <v>1730</v>
       </c>
       <c r="J63" t="n">
-        <v>2.0915690933872</v>
+        <v>2.09156909338722</v>
       </c>
       <c r="K63" t="s">
         <v>1778</v>
@@ -21912,7 +21912,7 @@
         <v>1730</v>
       </c>
       <c r="J64" t="n">
-        <v>2.0915690933872</v>
+        <v>2.09156909338722</v>
       </c>
       <c r="K64" t="s">
         <v>1779</v>
@@ -21947,7 +21947,7 @@
         <v>1730</v>
       </c>
       <c r="J65" t="n">
-        <v>2.07548818878937</v>
+        <v>2.07548818878945</v>
       </c>
       <c r="K65" t="s">
         <v>1782</v>
@@ -21982,7 +21982,7 @@
         <v>1730</v>
       </c>
       <c r="J66" t="n">
-        <v>2.07548818878937</v>
+        <v>2.07548818878945</v>
       </c>
       <c r="K66" t="s">
         <v>1783</v>
@@ -22017,7 +22017,7 @@
         <v>1730</v>
       </c>
       <c r="J67" t="n">
-        <v>2.07548818878937</v>
+        <v>2.07548818878945</v>
       </c>
       <c r="K67" t="s">
         <v>1784</v>
@@ -22052,7 +22052,7 @@
         <v>1730</v>
       </c>
       <c r="J68" t="n">
-        <v>2.07168225087733</v>
+        <v>2.07168225087764</v>
       </c>
       <c r="K68" t="s">
         <v>1787</v>
@@ -22087,7 +22087,7 @@
         <v>1730</v>
       </c>
       <c r="J69" t="n">
-        <v>2.07168225087733</v>
+        <v>2.07168225087764</v>
       </c>
       <c r="K69" t="s">
         <v>1788</v>
@@ -22122,7 +22122,7 @@
         <v>1730</v>
       </c>
       <c r="J70" t="n">
-        <v>2.07168225087733</v>
+        <v>2.07168225087764</v>
       </c>
       <c r="K70" t="s">
         <v>1789</v>
@@ -22157,7 +22157,7 @@
         <v>1730</v>
       </c>
       <c r="J71" t="n">
-        <v>2.05497795180014</v>
+        <v>2.05497795180055</v>
       </c>
       <c r="K71" t="s">
         <v>1792</v>
@@ -22192,7 +22192,7 @@
         <v>1730</v>
       </c>
       <c r="J72" t="n">
-        <v>2.05497795180014</v>
+        <v>2.05497795180055</v>
       </c>
       <c r="K72" t="s">
         <v>1793</v>
@@ -22227,7 +22227,7 @@
         <v>1730</v>
       </c>
       <c r="J73" t="n">
-        <v>2.05497795180014</v>
+        <v>2.05497795180055</v>
       </c>
       <c r="K73" t="s">
         <v>1794</v>
@@ -22262,7 +22262,7 @@
         <v>1730</v>
       </c>
       <c r="J74" t="n">
-        <v>2.03147723009378</v>
+        <v>2.03147723009388</v>
       </c>
       <c r="K74" t="s">
         <v>1797</v>
@@ -22297,7 +22297,7 @@
         <v>1730</v>
       </c>
       <c r="J75" t="n">
-        <v>2.03147723009378</v>
+        <v>2.03147723009388</v>
       </c>
       <c r="K75" t="s">
         <v>1798</v>
@@ -22332,7 +22332,7 @@
         <v>1730</v>
       </c>
       <c r="J76" t="n">
-        <v>2.03147723009378</v>
+        <v>2.03147723009388</v>
       </c>
       <c r="K76" t="s">
         <v>1799</v>
@@ -22367,7 +22367,7 @@
         <v>1730</v>
       </c>
       <c r="J77" t="n">
-        <v>2.01196089901776</v>
+        <v>2.01196089901808</v>
       </c>
       <c r="K77" t="s">
         <v>1802</v>
@@ -22402,7 +22402,7 @@
         <v>1730</v>
       </c>
       <c r="J78" t="n">
-        <v>2.01196089901776</v>
+        <v>2.01196089901808</v>
       </c>
       <c r="K78" t="s">
         <v>1803</v>
@@ -22437,7 +22437,7 @@
         <v>1730</v>
       </c>
       <c r="J79" t="n">
-        <v>2.01196089901776</v>
+        <v>2.01196089901808</v>
       </c>
       <c r="K79" t="s">
         <v>1804</v>
@@ -22472,7 +22472,7 @@
         <v>1730</v>
       </c>
       <c r="J80" t="n">
-        <v>1.99634807012949</v>
+        <v>1.99634807012989</v>
       </c>
       <c r="K80" t="s">
         <v>1805</v>
@@ -22507,7 +22507,7 @@
         <v>1730</v>
       </c>
       <c r="J81" t="n">
-        <v>1.99634807012949</v>
+        <v>1.99634807012989</v>
       </c>
       <c r="K81" t="s">
         <v>1806</v>
@@ -22542,7 +22542,7 @@
         <v>1730</v>
       </c>
       <c r="J82" t="n">
-        <v>1.99634807012949</v>
+        <v>1.99634807012989</v>
       </c>
       <c r="K82" t="s">
         <v>1807</v>
@@ -22577,7 +22577,7 @@
         <v>1730</v>
       </c>
       <c r="J83" t="n">
-        <v>1.94008386869785</v>
+        <v>1.94008386869808</v>
       </c>
       <c r="K83" t="s">
         <v>1808</v>
@@ -22612,7 +22612,7 @@
         <v>1730</v>
       </c>
       <c r="J84" t="n">
-        <v>1.94008386869785</v>
+        <v>1.94008386869808</v>
       </c>
       <c r="K84" t="s">
         <v>1809</v>
@@ -22647,7 +22647,7 @@
         <v>1730</v>
       </c>
       <c r="J85" t="n">
-        <v>1.94008386869785</v>
+        <v>1.94008386869808</v>
       </c>
       <c r="K85" t="s">
         <v>1810</v>
@@ -22682,7 +22682,7 @@
         <v>1730</v>
       </c>
       <c r="J86" t="n">
-        <v>1.92761480476687</v>
+        <v>1.92761480476712</v>
       </c>
       <c r="K86" t="s">
         <v>1811</v>
@@ -22717,7 +22717,7 @@
         <v>1730</v>
       </c>
       <c r="J87" t="n">
-        <v>1.92761480476687</v>
+        <v>1.92761480476712</v>
       </c>
       <c r="K87" t="s">
         <v>1812</v>
@@ -22752,7 +22752,7 @@
         <v>1730</v>
       </c>
       <c r="J88" t="n">
-        <v>1.92761480476687</v>
+        <v>1.92761480476712</v>
       </c>
       <c r="K88" t="s">
         <v>1813</v>
@@ -22787,7 +22787,7 @@
         <v>1730</v>
       </c>
       <c r="J89" t="n">
-        <v>1.90448120540577</v>
+        <v>1.90448120540602</v>
       </c>
       <c r="K89" t="s">
         <v>1816</v>
@@ -22822,7 +22822,7 @@
         <v>1730</v>
       </c>
       <c r="J90" t="n">
-        <v>1.90448120540577</v>
+        <v>1.90448120540602</v>
       </c>
       <c r="K90" t="s">
         <v>1817</v>
@@ -22857,7 +22857,7 @@
         <v>1730</v>
       </c>
       <c r="J91" t="n">
-        <v>1.90448120540577</v>
+        <v>1.90448120540602</v>
       </c>
       <c r="K91" t="s">
         <v>1818</v>
@@ -22892,7 +22892,7 @@
         <v>1730</v>
       </c>
       <c r="J92" t="n">
-        <v>1.88595021917732</v>
+        <v>1.88595021917705</v>
       </c>
       <c r="K92" t="s">
         <v>1821</v>
@@ -22927,7 +22927,7 @@
         <v>1730</v>
       </c>
       <c r="J93" t="n">
-        <v>1.88595021917732</v>
+        <v>1.88595021917705</v>
       </c>
       <c r="K93" t="s">
         <v>1822</v>
@@ -22962,7 +22962,7 @@
         <v>1730</v>
       </c>
       <c r="J94" t="n">
-        <v>1.88595021917732</v>
+        <v>1.88595021917705</v>
       </c>
       <c r="K94" t="s">
         <v>1823</v>
@@ -22997,7 +22997,7 @@
         <v>1730</v>
       </c>
       <c r="J95" t="n">
-        <v>1.87674960064076</v>
+        <v>1.87674960064129</v>
       </c>
       <c r="K95" t="s">
         <v>1826</v>
@@ -23032,7 +23032,7 @@
         <v>1730</v>
       </c>
       <c r="J96" t="n">
-        <v>1.87674960064076</v>
+        <v>1.87674960064129</v>
       </c>
       <c r="K96" t="s">
         <v>1827</v>
@@ -23067,7 +23067,7 @@
         <v>1730</v>
       </c>
       <c r="J97" t="n">
-        <v>1.87674960064076</v>
+        <v>1.87674960064129</v>
       </c>
       <c r="K97" t="s">
         <v>1828</v>
@@ -23102,7 +23102,7 @@
         <v>1730</v>
       </c>
       <c r="J98" t="n">
-        <v>1.87418329431386</v>
+        <v>1.87418329431412</v>
       </c>
       <c r="K98" t="s">
         <v>1829</v>
@@ -23137,7 +23137,7 @@
         <v>1730</v>
       </c>
       <c r="J99" t="n">
-        <v>1.87418329431386</v>
+        <v>1.87418329431412</v>
       </c>
       <c r="K99" t="s">
         <v>1830</v>
@@ -23172,7 +23172,7 @@
         <v>1730</v>
       </c>
       <c r="J100" t="n">
-        <v>1.87418329431386</v>
+        <v>1.87418329431412</v>
       </c>
       <c r="K100" t="s">
         <v>1831</v>
@@ -23207,7 +23207,7 @@
         <v>1730</v>
       </c>
       <c r="J101" t="n">
-        <v>1.86881504902009</v>
+        <v>1.86881504902021</v>
       </c>
       <c r="K101" t="s">
         <v>1834</v>
@@ -23242,7 +23242,7 @@
         <v>1730</v>
       </c>
       <c r="J102" t="n">
-        <v>1.86881504902009</v>
+        <v>1.86881504902021</v>
       </c>
       <c r="K102" t="s">
         <v>1835</v>
@@ -23277,7 +23277,7 @@
         <v>1730</v>
       </c>
       <c r="J103" t="n">
-        <v>1.86881504902009</v>
+        <v>1.86881504902021</v>
       </c>
       <c r="K103" t="s">
         <v>1836</v>
@@ -23312,7 +23312,7 @@
         <v>1730</v>
       </c>
       <c r="J104" t="n">
-        <v>1.84754675542553</v>
+        <v>1.84754675542573</v>
       </c>
       <c r="K104" t="s">
         <v>1837</v>
@@ -23347,7 +23347,7 @@
         <v>1730</v>
       </c>
       <c r="J105" t="n">
-        <v>1.84754675542553</v>
+        <v>1.84754675542573</v>
       </c>
       <c r="K105" t="s">
         <v>1838</v>
@@ -23382,7 +23382,7 @@
         <v>1730</v>
       </c>
       <c r="J106" t="n">
-        <v>1.84754675542553</v>
+        <v>1.84754675542573</v>
       </c>
       <c r="K106" t="s">
         <v>1839</v>
@@ -23417,7 +23417,7 @@
         <v>1730</v>
       </c>
       <c r="J107" t="n">
-        <v>1.80921196132429</v>
+        <v>1.80921196132455</v>
       </c>
       <c r="K107" t="s">
         <v>1842</v>
@@ -23452,7 +23452,7 @@
         <v>1730</v>
       </c>
       <c r="J108" t="n">
-        <v>1.80921196132429</v>
+        <v>1.80921196132455</v>
       </c>
       <c r="K108" t="s">
         <v>1843</v>
@@ -23487,7 +23487,7 @@
         <v>1730</v>
       </c>
       <c r="J109" t="n">
-        <v>1.80921196132429</v>
+        <v>1.80921196132455</v>
       </c>
       <c r="K109" t="s">
         <v>1844</v>
@@ -23522,7 +23522,7 @@
         <v>1730</v>
       </c>
       <c r="J110" t="n">
-        <v>1.80654406290558</v>
+        <v>1.80654406290571</v>
       </c>
       <c r="K110" t="s">
         <v>1847</v>
@@ -23557,7 +23557,7 @@
         <v>1730</v>
       </c>
       <c r="J111" t="n">
-        <v>1.80654406290558</v>
+        <v>1.80654406290571</v>
       </c>
       <c r="K111" t="s">
         <v>1848</v>
@@ -23592,7 +23592,7 @@
         <v>1730</v>
       </c>
       <c r="J112" t="n">
-        <v>1.80654406290558</v>
+        <v>1.80654406290571</v>
       </c>
       <c r="K112" t="s">
         <v>1849</v>
@@ -23627,7 +23627,7 @@
         <v>1730</v>
       </c>
       <c r="J113" t="n">
-        <v>1.80408449810945</v>
+        <v>1.80408449810988</v>
       </c>
       <c r="K113" t="s">
         <v>1852</v>
@@ -23662,7 +23662,7 @@
         <v>1730</v>
       </c>
       <c r="J114" t="n">
-        <v>1.80408449810945</v>
+        <v>1.80408449810988</v>
       </c>
       <c r="K114" t="s">
         <v>1853</v>
@@ -23697,7 +23697,7 @@
         <v>1730</v>
       </c>
       <c r="J115" t="n">
-        <v>1.80408449810945</v>
+        <v>1.80408449810988</v>
       </c>
       <c r="K115" t="s">
         <v>1854</v>
@@ -23732,7 +23732,7 @@
         <v>1730</v>
       </c>
       <c r="J116" t="n">
-        <v>1.78698568574005</v>
+        <v>1.78698568574029</v>
       </c>
       <c r="K116" t="s">
         <v>1857</v>
@@ -23767,7 +23767,7 @@
         <v>1730</v>
       </c>
       <c r="J117" t="n">
-        <v>1.78698568574005</v>
+        <v>1.78698568574029</v>
       </c>
       <c r="K117" t="s">
         <v>1858</v>
@@ -23802,7 +23802,7 @@
         <v>1730</v>
       </c>
       <c r="J118" t="n">
-        <v>1.78698568574005</v>
+        <v>1.78698568574029</v>
       </c>
       <c r="K118" t="s">
         <v>1859</v>
@@ -23837,7 +23837,7 @@
         <v>1730</v>
       </c>
       <c r="J119" t="n">
-        <v>1.76781744881565</v>
+        <v>1.76781744881587</v>
       </c>
       <c r="K119" t="s">
         <v>1860</v>
@@ -23872,7 +23872,7 @@
         <v>1730</v>
       </c>
       <c r="J120" t="n">
-        <v>1.76781744881565</v>
+        <v>1.76781744881587</v>
       </c>
       <c r="K120" t="s">
         <v>1861</v>
@@ -23907,7 +23907,7 @@
         <v>1730</v>
       </c>
       <c r="J121" t="n">
-        <v>1.76781744881565</v>
+        <v>1.76781744881587</v>
       </c>
       <c r="K121" t="s">
         <v>1862</v>
@@ -23942,7 +23942,7 @@
         <v>1730</v>
       </c>
       <c r="J122" t="n">
-        <v>1.75726003359441</v>
+        <v>1.75726003359468</v>
       </c>
       <c r="K122" t="s">
         <v>1865</v>
@@ -23977,7 +23977,7 @@
         <v>1730</v>
       </c>
       <c r="J123" t="n">
-        <v>1.75726003359441</v>
+        <v>1.75726003359468</v>
       </c>
       <c r="K123" t="s">
         <v>1866</v>
@@ -24012,7 +24012,7 @@
         <v>1730</v>
       </c>
       <c r="J124" t="n">
-        <v>1.75726003359441</v>
+        <v>1.75726003359468</v>
       </c>
       <c r="K124" t="s">
         <v>1867</v>
@@ -24047,7 +24047,7 @@
         <v>1730</v>
       </c>
       <c r="J125" t="n">
-        <v>1.7550776276479</v>
+        <v>1.75507762764802</v>
       </c>
       <c r="K125" t="s">
         <v>1870</v>
@@ -24082,7 +24082,7 @@
         <v>1730</v>
       </c>
       <c r="J126" t="n">
-        <v>1.7550776276479</v>
+        <v>1.75507762764802</v>
       </c>
       <c r="K126" t="s">
         <v>1871</v>
@@ -24117,7 +24117,7 @@
         <v>1730</v>
       </c>
       <c r="J127" t="n">
-        <v>1.7550776276479</v>
+        <v>1.75507762764802</v>
       </c>
       <c r="K127" t="s">
         <v>1872</v>
@@ -24152,7 +24152,7 @@
         <v>1730</v>
       </c>
       <c r="J128" t="n">
-        <v>1.73599186659361</v>
+        <v>1.73599186659375</v>
       </c>
       <c r="K128" t="s">
         <v>1875</v>
@@ -24187,7 +24187,7 @@
         <v>1730</v>
       </c>
       <c r="J129" t="n">
-        <v>1.73599186659361</v>
+        <v>1.73599186659375</v>
       </c>
       <c r="K129" t="s">
         <v>1876</v>
@@ -24222,7 +24222,7 @@
         <v>1730</v>
       </c>
       <c r="J130" t="n">
-        <v>1.73599186659361</v>
+        <v>1.73599186659375</v>
       </c>
       <c r="K130" t="s">
         <v>1877</v>
@@ -24257,7 +24257,7 @@
         <v>1730</v>
       </c>
       <c r="J131" t="n">
-        <v>1.71074189407741</v>
+        <v>1.71074189407758</v>
       </c>
       <c r="K131" t="s">
         <v>1880</v>
@@ -24292,7 +24292,7 @@
         <v>1730</v>
       </c>
       <c r="J132" t="n">
-        <v>1.71074189407741</v>
+        <v>1.71074189407758</v>
       </c>
       <c r="K132" t="s">
         <v>1881</v>
@@ -24327,7 +24327,7 @@
         <v>1730</v>
       </c>
       <c r="J133" t="n">
-        <v>1.71074189407741</v>
+        <v>1.71074189407758</v>
       </c>
       <c r="K133" t="s">
         <v>1882</v>
@@ -24362,7 +24362,7 @@
         <v>1730</v>
       </c>
       <c r="J134" t="n">
-        <v>1.70673304424475</v>
+        <v>1.7067330442449</v>
       </c>
       <c r="K134" t="s">
         <v>1885</v>
@@ -24397,7 +24397,7 @@
         <v>1730</v>
       </c>
       <c r="J135" t="n">
-        <v>1.70673304424475</v>
+        <v>1.7067330442449</v>
       </c>
       <c r="K135" t="s">
         <v>1886</v>
@@ -24432,7 +24432,7 @@
         <v>1730</v>
       </c>
       <c r="J136" t="n">
-        <v>1.70673304424475</v>
+        <v>1.7067330442449</v>
       </c>
       <c r="K136" t="s">
         <v>1887</v>
@@ -24467,7 +24467,7 @@
         <v>1730</v>
       </c>
       <c r="J137" t="n">
-        <v>1.70536858947769</v>
+        <v>1.70536858947799</v>
       </c>
       <c r="K137" t="s">
         <v>1888</v>
@@ -24502,7 +24502,7 @@
         <v>1730</v>
       </c>
       <c r="J138" t="n">
-        <v>1.70536858947769</v>
+        <v>1.70536858947799</v>
       </c>
       <c r="K138" t="s">
         <v>1889</v>
@@ -24537,7 +24537,7 @@
         <v>1730</v>
       </c>
       <c r="J139" t="n">
-        <v>1.70536858947769</v>
+        <v>1.70536858947799</v>
       </c>
       <c r="K139" t="s">
         <v>1890</v>
@@ -24572,7 +24572,7 @@
         <v>1730</v>
       </c>
       <c r="J140" t="n">
-        <v>1.60802293683883</v>
+        <v>1.60802293683885</v>
       </c>
       <c r="K140" t="s">
         <v>1891</v>
@@ -24607,7 +24607,7 @@
         <v>1730</v>
       </c>
       <c r="J141" t="n">
-        <v>1.60802293683883</v>
+        <v>1.60802293683885</v>
       </c>
       <c r="K141" t="s">
         <v>1892</v>
@@ -24642,7 +24642,7 @@
         <v>1730</v>
       </c>
       <c r="J142" t="n">
-        <v>1.60802293683883</v>
+        <v>1.60802293683885</v>
       </c>
       <c r="K142" t="s">
         <v>1893</v>
@@ -24677,7 +24677,7 @@
         <v>1730</v>
       </c>
       <c r="J143" t="n">
-        <v>1.52966416562515</v>
+        <v>1.52966416562524</v>
       </c>
       <c r="K143" t="s">
         <v>1896</v>
@@ -24712,7 +24712,7 @@
         <v>1730</v>
       </c>
       <c r="J144" t="n">
-        <v>1.52966416562515</v>
+        <v>1.52966416562524</v>
       </c>
       <c r="K144" t="s">
         <v>1897</v>
@@ -24747,7 +24747,7 @@
         <v>1730</v>
       </c>
       <c r="J145" t="n">
-        <v>1.52966416562515</v>
+        <v>1.52966416562524</v>
       </c>
       <c r="K145" t="s">
         <v>1898</v>
@@ -24782,7 +24782,7 @@
         <v>1730</v>
       </c>
       <c r="J146" t="n">
-        <v>-1.65866969854636</v>
+        <v>-1.65866969854619</v>
       </c>
       <c r="K146" t="s">
         <v>1901</v>
@@ -24817,7 +24817,7 @@
         <v>1730</v>
       </c>
       <c r="J147" t="n">
-        <v>-1.65866969854636</v>
+        <v>-1.65866969854619</v>
       </c>
       <c r="K147" t="s">
         <v>1902</v>
@@ -24852,7 +24852,7 @@
         <v>1730</v>
       </c>
       <c r="J148" t="n">
-        <v>-1.65866969854636</v>
+        <v>-1.65866969854619</v>
       </c>
       <c r="K148" t="s">
         <v>1903</v>
@@ -24887,7 +24887,7 @@
         <v>1730</v>
       </c>
       <c r="J149" t="n">
-        <v>-1.71179552644798</v>
+        <v>-1.71179552644785</v>
       </c>
       <c r="K149" t="s">
         <v>1904</v>
@@ -24922,7 +24922,7 @@
         <v>1730</v>
       </c>
       <c r="J150" t="n">
-        <v>-1.71179552644798</v>
+        <v>-1.71179552644785</v>
       </c>
       <c r="K150" t="s">
         <v>1905</v>
@@ -24957,7 +24957,7 @@
         <v>1730</v>
       </c>
       <c r="J151" t="n">
-        <v>-1.71179552644798</v>
+        <v>-1.71179552644785</v>
       </c>
       <c r="K151" t="s">
         <v>1906</v>
@@ -24992,7 +24992,7 @@
         <v>1730</v>
       </c>
       <c r="J152" t="n">
-        <v>-1.86289506356947</v>
+        <v>-1.86289506356975</v>
       </c>
       <c r="K152" t="s">
         <v>1909</v>
@@ -25027,7 +25027,7 @@
         <v>1730</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.86289506356947</v>
+        <v>-1.86289506356975</v>
       </c>
       <c r="K153" t="s">
         <v>1910</v>
@@ -25062,7 +25062,7 @@
         <v>1730</v>
       </c>
       <c r="J154" t="n">
-        <v>-1.86289506356947</v>
+        <v>-1.86289506356975</v>
       </c>
       <c r="K154" t="s">
         <v>1911</v>
@@ -25097,7 +25097,7 @@
         <v>1730</v>
       </c>
       <c r="J155" t="n">
-        <v>-1.87604500151868</v>
+        <v>-1.87604500151845</v>
       </c>
       <c r="K155" t="s">
         <v>1912</v>
@@ -25132,7 +25132,7 @@
         <v>1730</v>
       </c>
       <c r="J156" t="n">
-        <v>-1.87604500151868</v>
+        <v>-1.87604500151845</v>
       </c>
       <c r="K156" t="s">
         <v>1913</v>
@@ -25167,7 +25167,7 @@
         <v>1730</v>
       </c>
       <c r="J157" t="n">
-        <v>-1.87604500151868</v>
+        <v>-1.87604500151845</v>
       </c>
       <c r="K157" t="s">
         <v>1914</v>
@@ -25307,7 +25307,7 @@
         <v>1730</v>
       </c>
       <c r="J161" t="n">
-        <v>-1.90988159444275</v>
+        <v>-1.90988159444252</v>
       </c>
       <c r="K161" t="s">
         <v>1922</v>
@@ -25342,7 +25342,7 @@
         <v>1730</v>
       </c>
       <c r="J162" t="n">
-        <v>-1.90988159444275</v>
+        <v>-1.90988159444252</v>
       </c>
       <c r="K162" t="s">
         <v>1923</v>
@@ -25377,7 +25377,7 @@
         <v>1730</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.90988159444275</v>
+        <v>-1.90988159444252</v>
       </c>
       <c r="K163" t="s">
         <v>1924</v>
@@ -25412,7 +25412,7 @@
         <v>1730</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.38137667499684</v>
+        <v>-2.38137667499657</v>
       </c>
       <c r="K164" t="s">
         <v>1925</v>
@@ -25447,7 +25447,7 @@
         <v>1730</v>
       </c>
       <c r="J165" t="n">
-        <v>-2.38137667499684</v>
+        <v>-2.38137667499657</v>
       </c>
       <c r="K165" t="s">
         <v>1926</v>
@@ -25482,7 +25482,7 @@
         <v>1730</v>
       </c>
       <c r="J166" t="n">
-        <v>-2.38137667499684</v>
+        <v>-2.38137667499657</v>
       </c>
       <c r="K166" t="s">
         <v>1927</v>
@@ -25517,7 +25517,7 @@
         <v>1730</v>
       </c>
       <c r="J167" t="n">
-        <v>-2.4198780259265</v>
+        <v>-2.41987802592629</v>
       </c>
       <c r="K167" t="s">
         <v>1930</v>
@@ -25552,7 +25552,7 @@
         <v>1730</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.4198780259265</v>
+        <v>-2.41987802592629</v>
       </c>
       <c r="K168" t="s">
         <v>1931</v>
@@ -25587,7 +25587,7 @@
         <v>1730</v>
       </c>
       <c r="J169" t="n">
-        <v>-2.4198780259265</v>
+        <v>-2.41987802592629</v>
       </c>
       <c r="K169" t="s">
         <v>1932</v>
@@ -25622,7 +25622,7 @@
         <v>1730</v>
       </c>
       <c r="J170" t="n">
-        <v>-2.76736684982947</v>
+        <v>-2.76736684982922</v>
       </c>
       <c r="K170" t="s">
         <v>1935</v>
@@ -25657,7 +25657,7 @@
         <v>1730</v>
       </c>
       <c r="J171" t="n">
-        <v>-2.76736684982947</v>
+        <v>-2.76736684982922</v>
       </c>
       <c r="K171" t="s">
         <v>1936</v>
@@ -25692,7 +25692,7 @@
         <v>1730</v>
       </c>
       <c r="J172" t="n">
-        <v>-2.76736684982947</v>
+        <v>-2.76736684982922</v>
       </c>
       <c r="K172" t="s">
         <v>1937</v>
@@ -25727,7 +25727,7 @@
         <v>1730</v>
       </c>
       <c r="J173" t="n">
-        <v>-2.90152627673099</v>
+        <v>-2.90152627673059</v>
       </c>
       <c r="K173" t="s">
         <v>1940</v>
@@ -25762,7 +25762,7 @@
         <v>1730</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.90152627673099</v>
+        <v>-2.90152627673059</v>
       </c>
       <c r="K174" t="s">
         <v>1941</v>
@@ -25797,7 +25797,7 @@
         <v>1730</v>
       </c>
       <c r="J175" t="n">
-        <v>-2.90152627673099</v>
+        <v>-2.90152627673059</v>
       </c>
       <c r="K175" t="s">
         <v>1942</v>
@@ -25832,7 +25832,7 @@
         <v>1730</v>
       </c>
       <c r="J176" t="n">
-        <v>-3.03190644796132</v>
+        <v>-3.03190644796079</v>
       </c>
       <c r="K176" t="s">
         <v>1943</v>
@@ -25867,7 +25867,7 @@
         <v>1730</v>
       </c>
       <c r="J177" t="n">
-        <v>-3.03190644796132</v>
+        <v>-3.03190644796079</v>
       </c>
       <c r="K177" t="s">
         <v>1944</v>
@@ -25902,7 +25902,7 @@
         <v>1730</v>
       </c>
       <c r="J178" t="n">
-        <v>-3.03190644796132</v>
+        <v>-3.03190644796079</v>
       </c>
       <c r="K178" t="s">
         <v>1945</v>
@@ -25937,7 +25937,7 @@
         <v>1730</v>
       </c>
       <c r="J179" t="n">
-        <v>-3.05659126973461</v>
+        <v>-3.05659126973403</v>
       </c>
       <c r="K179" t="s">
         <v>1946</v>
@@ -25972,7 +25972,7 @@
         <v>1730</v>
       </c>
       <c r="J180" t="n">
-        <v>-3.05659126973461</v>
+        <v>-3.05659126973403</v>
       </c>
       <c r="K180" t="s">
         <v>1947</v>
@@ -26007,7 +26007,7 @@
         <v>1730</v>
       </c>
       <c r="J181" t="n">
-        <v>-3.05659126973461</v>
+        <v>-3.05659126973403</v>
       </c>
       <c r="K181" t="s">
         <v>1942</v>
@@ -26042,7 +26042,7 @@
         <v>1730</v>
       </c>
       <c r="J182" t="n">
-        <v>-3.23043170284295</v>
+        <v>-3.23043170284236</v>
       </c>
       <c r="K182" t="s">
         <v>1940</v>
@@ -26077,7 +26077,7 @@
         <v>1730</v>
       </c>
       <c r="J183" t="n">
-        <v>-3.23043170284295</v>
+        <v>-3.23043170284236</v>
       </c>
       <c r="K183" t="s">
         <v>1948</v>
@@ -26112,7 +26112,7 @@
         <v>1730</v>
       </c>
       <c r="J184" t="n">
-        <v>-3.23043170284295</v>
+        <v>-3.23043170284236</v>
       </c>
       <c r="K184" t="s">
         <v>1942</v>
@@ -26147,7 +26147,7 @@
         <v>1730</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.2433151661988</v>
+        <v>-3.24331516619826</v>
       </c>
       <c r="K185" t="s">
         <v>1949</v>
@@ -26182,7 +26182,7 @@
         <v>1730</v>
       </c>
       <c r="J186" t="n">
-        <v>-3.2433151661988</v>
+        <v>-3.24331516619826</v>
       </c>
       <c r="K186" t="s">
         <v>1950</v>
@@ -26217,7 +26217,7 @@
         <v>1730</v>
       </c>
       <c r="J187" t="n">
-        <v>-3.2433151661988</v>
+        <v>-3.24331516619826</v>
       </c>
       <c r="K187" t="s">
         <v>1951</v>
@@ -26252,7 +26252,7 @@
         <v>1954</v>
       </c>
       <c r="J188" t="n">
-        <v>2.82205965011805</v>
+        <v>2.82205965011776</v>
       </c>
       <c r="K188" t="s">
         <v>1955</v>
@@ -26287,7 +26287,7 @@
         <v>1954</v>
       </c>
       <c r="J189" t="n">
-        <v>2.82205965011805</v>
+        <v>2.82205965011776</v>
       </c>
       <c r="K189" t="s">
         <v>1956</v>
@@ -26322,7 +26322,7 @@
         <v>1954</v>
       </c>
       <c r="J190" t="n">
-        <v>2.82205965011805</v>
+        <v>2.82205965011776</v>
       </c>
       <c r="K190" t="s">
         <v>1957</v>
@@ -26357,7 +26357,7 @@
         <v>1954</v>
       </c>
       <c r="J191" t="n">
-        <v>2.70138320368777</v>
+        <v>2.70138320368754</v>
       </c>
       <c r="K191" t="s">
         <v>1960</v>
@@ -26392,7 +26392,7 @@
         <v>1954</v>
       </c>
       <c r="J192" t="n">
-        <v>2.70138320368777</v>
+        <v>2.70138320368754</v>
       </c>
       <c r="K192" t="s">
         <v>1961</v>
@@ -26427,7 +26427,7 @@
         <v>1954</v>
       </c>
       <c r="J193" t="n">
-        <v>2.70138320368777</v>
+        <v>2.70138320368754</v>
       </c>
       <c r="K193" t="s">
         <v>1962</v>
@@ -26462,7 +26462,7 @@
         <v>1954</v>
       </c>
       <c r="J194" t="n">
-        <v>2.60643135294245</v>
+        <v>2.60643135294238</v>
       </c>
       <c r="K194" t="s">
         <v>1964</v>
@@ -26497,7 +26497,7 @@
         <v>1954</v>
       </c>
       <c r="J195" t="n">
-        <v>2.60643135294245</v>
+        <v>2.60643135294238</v>
       </c>
       <c r="K195" t="s">
         <v>1965</v>
@@ -26532,7 +26532,7 @@
         <v>1954</v>
       </c>
       <c r="J196" t="n">
-        <v>2.60643135294245</v>
+        <v>2.60643135294238</v>
       </c>
       <c r="K196" t="s">
         <v>1966</v>
@@ -26567,7 +26567,7 @@
         <v>1954</v>
       </c>
       <c r="J197" t="n">
-        <v>2.05273632482049</v>
+        <v>2.0527363248205</v>
       </c>
       <c r="K197" t="s">
         <v>1969</v>
@@ -26602,7 +26602,7 @@
         <v>1954</v>
       </c>
       <c r="J198" t="n">
-        <v>2.05273632482049</v>
+        <v>2.0527363248205</v>
       </c>
       <c r="K198" t="s">
         <v>1970</v>
@@ -26637,7 +26637,7 @@
         <v>1954</v>
       </c>
       <c r="J199" t="n">
-        <v>2.05273632482049</v>
+        <v>2.0527363248205</v>
       </c>
       <c r="K199" t="s">
         <v>1971</v>
@@ -26672,7 +26672,7 @@
         <v>1954</v>
       </c>
       <c r="J200" t="n">
-        <v>1.85445195494392</v>
+        <v>1.85445195494361</v>
       </c>
       <c r="K200" t="s">
         <v>1974</v>
@@ -26707,7 +26707,7 @@
         <v>1954</v>
       </c>
       <c r="J201" t="n">
-        <v>1.85445195494392</v>
+        <v>1.85445195494361</v>
       </c>
       <c r="K201" t="s">
         <v>1975</v>
@@ -26742,7 +26742,7 @@
         <v>1954</v>
       </c>
       <c r="J202" t="n">
-        <v>1.85445195494392</v>
+        <v>1.85445195494361</v>
       </c>
       <c r="K202" t="s">
         <v>1976</v>
@@ -26777,7 +26777,7 @@
         <v>1954</v>
       </c>
       <c r="J203" t="n">
-        <v>1.83381491401663</v>
+        <v>1.83381491401674</v>
       </c>
       <c r="K203" t="s">
         <v>1977</v>
@@ -26812,7 +26812,7 @@
         <v>1954</v>
       </c>
       <c r="J204" t="n">
-        <v>1.83381491401663</v>
+        <v>1.83381491401674</v>
       </c>
       <c r="K204" t="s">
         <v>1978</v>
@@ -26847,7 +26847,7 @@
         <v>1954</v>
       </c>
       <c r="J205" t="n">
-        <v>1.83381491401663</v>
+        <v>1.83381491401674</v>
       </c>
       <c r="K205" t="s">
         <v>1979</v>
@@ -26882,7 +26882,7 @@
         <v>1954</v>
       </c>
       <c r="J206" t="n">
-        <v>1.81930360700978</v>
+        <v>1.81930360700989</v>
       </c>
       <c r="K206" t="s">
         <v>1826</v>
@@ -26917,7 +26917,7 @@
         <v>1954</v>
       </c>
       <c r="J207" t="n">
-        <v>1.81930360700978</v>
+        <v>1.81930360700989</v>
       </c>
       <c r="K207" t="s">
         <v>1981</v>
@@ -26952,7 +26952,7 @@
         <v>1954</v>
       </c>
       <c r="J208" t="n">
-        <v>1.81930360700978</v>
+        <v>1.81930360700989</v>
       </c>
       <c r="K208" t="s">
         <v>1982</v>
@@ -26987,7 +26987,7 @@
         <v>1954</v>
       </c>
       <c r="J209" t="n">
-        <v>1.76327661915098</v>
+        <v>1.76327661915103</v>
       </c>
       <c r="K209" t="s">
         <v>1985</v>
@@ -27022,7 +27022,7 @@
         <v>1954</v>
       </c>
       <c r="J210" t="n">
-        <v>1.76327661915098</v>
+        <v>1.76327661915103</v>
       </c>
       <c r="K210" t="s">
         <v>1986</v>
@@ -27057,7 +27057,7 @@
         <v>1954</v>
       </c>
       <c r="J211" t="n">
-        <v>1.76327661915098</v>
+        <v>1.76327661915103</v>
       </c>
       <c r="K211" t="s">
         <v>1987</v>
@@ -27092,7 +27092,7 @@
         <v>1954</v>
       </c>
       <c r="J212" t="n">
-        <v>1.73147725686328</v>
+        <v>1.73147725686341</v>
       </c>
       <c r="K212" t="s">
         <v>1989</v>
@@ -27127,7 +27127,7 @@
         <v>1954</v>
       </c>
       <c r="J213" t="n">
-        <v>1.73147725686328</v>
+        <v>1.73147725686341</v>
       </c>
       <c r="K213" t="s">
         <v>1990</v>
@@ -27162,7 +27162,7 @@
         <v>1954</v>
       </c>
       <c r="J214" t="n">
-        <v>1.73147725686328</v>
+        <v>1.73147725686341</v>
       </c>
       <c r="K214" t="s">
         <v>1991</v>
@@ -27197,7 +27197,7 @@
         <v>1954</v>
       </c>
       <c r="J215" t="n">
-        <v>-1.68827317848766</v>
+        <v>-1.68827317848786</v>
       </c>
       <c r="K215" t="s">
         <v>1994</v>
@@ -27232,7 +27232,7 @@
         <v>1954</v>
       </c>
       <c r="J216" t="n">
-        <v>-1.68827317848766</v>
+        <v>-1.68827317848786</v>
       </c>
       <c r="K216" t="s">
         <v>1995</v>
@@ -27267,7 +27267,7 @@
         <v>1954</v>
       </c>
       <c r="J217" t="n">
-        <v>-1.68827317848766</v>
+        <v>-1.68827317848786</v>
       </c>
       <c r="K217" t="s">
         <v>1996</v>
@@ -27302,7 +27302,7 @@
         <v>1954</v>
       </c>
       <c r="J218" t="n">
-        <v>-1.70079970935201</v>
+        <v>-1.70079970935214</v>
       </c>
       <c r="K218" t="s">
         <v>1997</v>
@@ -27337,7 +27337,7 @@
         <v>1954</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.70079970935201</v>
+        <v>-1.70079970935214</v>
       </c>
       <c r="K219" t="s">
         <v>1998</v>
@@ -27372,7 +27372,7 @@
         <v>1954</v>
       </c>
       <c r="J220" t="n">
-        <v>-1.70079970935201</v>
+        <v>-1.70079970935214</v>
       </c>
       <c r="K220" t="s">
         <v>1999</v>
@@ -27407,7 +27407,7 @@
         <v>1954</v>
       </c>
       <c r="J221" t="n">
-        <v>-1.71154340966622</v>
+        <v>-1.71154340966643</v>
       </c>
       <c r="K221" t="s">
         <v>2002</v>
@@ -27442,7 +27442,7 @@
         <v>1954</v>
       </c>
       <c r="J222" t="n">
-        <v>-1.71154340966622</v>
+        <v>-1.71154340966643</v>
       </c>
       <c r="K222" t="s">
         <v>2003</v>
@@ -27477,7 +27477,7 @@
         <v>1954</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.71154340966622</v>
+        <v>-1.71154340966643</v>
       </c>
       <c r="K223" t="s">
         <v>2004</v>
@@ -27512,7 +27512,7 @@
         <v>1954</v>
       </c>
       <c r="J224" t="n">
-        <v>-1.76641994943184</v>
+        <v>-1.76641994943178</v>
       </c>
       <c r="K224" t="s">
         <v>2006</v>
@@ -27547,7 +27547,7 @@
         <v>1954</v>
       </c>
       <c r="J225" t="n">
-        <v>-1.76641994943184</v>
+        <v>-1.76641994943178</v>
       </c>
       <c r="K225" t="s">
         <v>2007</v>
@@ -27582,7 +27582,7 @@
         <v>1954</v>
       </c>
       <c r="J226" t="n">
-        <v>-1.76641994943184</v>
+        <v>-1.76641994943178</v>
       </c>
       <c r="K226" t="s">
         <v>2008</v>
@@ -27617,7 +27617,7 @@
         <v>1954</v>
       </c>
       <c r="J227" t="n">
-        <v>-1.79116644677687</v>
+        <v>-1.791166446777</v>
       </c>
       <c r="K227" t="s">
         <v>2011</v>
@@ -27652,7 +27652,7 @@
         <v>1954</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.79116644677687</v>
+        <v>-1.791166446777</v>
       </c>
       <c r="K228" t="s">
         <v>2012</v>
@@ -27687,7 +27687,7 @@
         <v>1954</v>
       </c>
       <c r="J229" t="n">
-        <v>-1.79116644677687</v>
+        <v>-1.791166446777</v>
       </c>
       <c r="K229" t="s">
         <v>2013</v>
@@ -27722,7 +27722,7 @@
         <v>1954</v>
       </c>
       <c r="J230" t="n">
-        <v>-1.82626912896525</v>
+        <v>-1.82626912896524</v>
       </c>
       <c r="K230" t="s">
         <v>2016</v>
@@ -27757,7 +27757,7 @@
         <v>1954</v>
       </c>
       <c r="J231" t="n">
-        <v>-1.82626912896525</v>
+        <v>-1.82626912896524</v>
       </c>
       <c r="K231" t="s">
         <v>2017</v>
@@ -27792,7 +27792,7 @@
         <v>1954</v>
       </c>
       <c r="J232" t="n">
-        <v>-1.82626912896525</v>
+        <v>-1.82626912896524</v>
       </c>
       <c r="K232" t="s">
         <v>2018</v>
@@ -27827,7 +27827,7 @@
         <v>1954</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.85326099966338</v>
+        <v>-1.85326099966354</v>
       </c>
       <c r="K233" t="s">
         <v>2021</v>
@@ -27862,7 +27862,7 @@
         <v>1954</v>
       </c>
       <c r="J234" t="n">
-        <v>-1.85326099966338</v>
+        <v>-1.85326099966354</v>
       </c>
       <c r="K234" t="s">
         <v>2022</v>
@@ -27897,7 +27897,7 @@
         <v>1954</v>
       </c>
       <c r="J235" t="n">
-        <v>-1.85326099966338</v>
+        <v>-1.85326099966354</v>
       </c>
       <c r="K235" t="s">
         <v>2023</v>
@@ -27932,7 +27932,7 @@
         <v>1954</v>
       </c>
       <c r="J236" t="n">
-        <v>-1.87982205250958</v>
+        <v>-1.87982205250964</v>
       </c>
       <c r="K236" t="s">
         <v>2024</v>
@@ -27967,7 +27967,7 @@
         <v>1954</v>
       </c>
       <c r="J237" t="n">
-        <v>-1.87982205250958</v>
+        <v>-1.87982205250964</v>
       </c>
       <c r="K237" t="s">
         <v>2025</v>
@@ -28002,7 +28002,7 @@
         <v>1954</v>
       </c>
       <c r="J238" t="n">
-        <v>-1.87982205250958</v>
+        <v>-1.87982205250964</v>
       </c>
       <c r="K238" t="s">
         <v>2026</v>
@@ -28037,7 +28037,7 @@
         <v>1954</v>
       </c>
       <c r="J239" t="n">
-        <v>-1.88048899282776</v>
+        <v>-1.88048899282768</v>
       </c>
       <c r="K239" t="s">
         <v>2029</v>
@@ -28072,7 +28072,7 @@
         <v>1954</v>
       </c>
       <c r="J240" t="n">
-        <v>-1.88048899282776</v>
+        <v>-1.88048899282768</v>
       </c>
       <c r="K240" t="s">
         <v>2030</v>
@@ -28107,7 +28107,7 @@
         <v>1954</v>
       </c>
       <c r="J241" t="n">
-        <v>-1.88048899282776</v>
+        <v>-1.88048899282768</v>
       </c>
       <c r="K241" t="s">
         <v>2031</v>
@@ -28142,7 +28142,7 @@
         <v>1954</v>
       </c>
       <c r="J242" t="n">
-        <v>-1.89362159025333</v>
+        <v>-1.89362159025359</v>
       </c>
       <c r="K242" t="s">
         <v>2032</v>
@@ -28177,7 +28177,7 @@
         <v>1954</v>
       </c>
       <c r="J243" t="n">
-        <v>-1.89362159025333</v>
+        <v>-1.89362159025359</v>
       </c>
       <c r="K243" t="s">
         <v>2033</v>
@@ -28212,7 +28212,7 @@
         <v>1954</v>
       </c>
       <c r="J244" t="n">
-        <v>-1.89362159025333</v>
+        <v>-1.89362159025359</v>
       </c>
       <c r="K244" t="s">
         <v>2034</v>
@@ -28247,7 +28247,7 @@
         <v>1954</v>
       </c>
       <c r="J245" t="n">
-        <v>-1.89608514196756</v>
+        <v>-1.89608514196774</v>
       </c>
       <c r="K245" t="s">
         <v>2037</v>
@@ -28282,7 +28282,7 @@
         <v>1954</v>
       </c>
       <c r="J246" t="n">
-        <v>-1.89608514196756</v>
+        <v>-1.89608514196774</v>
       </c>
       <c r="K246" t="s">
         <v>2038</v>
@@ -28317,7 +28317,7 @@
         <v>1954</v>
       </c>
       <c r="J247" t="n">
-        <v>-1.89608514196756</v>
+        <v>-1.89608514196774</v>
       </c>
       <c r="K247" t="s">
         <v>2039</v>
@@ -28352,7 +28352,7 @@
         <v>1954</v>
       </c>
       <c r="J248" t="n">
-        <v>-1.89630856400753</v>
+        <v>-1.89630856400762</v>
       </c>
       <c r="K248" t="s">
         <v>2040</v>
@@ -28387,7 +28387,7 @@
         <v>1954</v>
       </c>
       <c r="J249" t="n">
-        <v>-1.89630856400753</v>
+        <v>-1.89630856400762</v>
       </c>
       <c r="K249" t="s">
         <v>2041</v>
@@ -28422,7 +28422,7 @@
         <v>1954</v>
       </c>
       <c r="J250" t="n">
-        <v>-1.89630856400753</v>
+        <v>-1.89630856400762</v>
       </c>
       <c r="K250" t="s">
         <v>2042</v>
@@ -28457,7 +28457,7 @@
         <v>1954</v>
       </c>
       <c r="J251" t="n">
-        <v>-1.90626246941752</v>
+        <v>-1.90626246941762</v>
       </c>
       <c r="K251" t="s">
         <v>2045</v>
@@ -28492,7 +28492,7 @@
         <v>1954</v>
       </c>
       <c r="J252" t="n">
-        <v>-1.90626246941752</v>
+        <v>-1.90626246941762</v>
       </c>
       <c r="K252" t="s">
         <v>2046</v>
@@ -28527,7 +28527,7 @@
         <v>1954</v>
       </c>
       <c r="J253" t="n">
-        <v>-1.90626246941752</v>
+        <v>-1.90626246941762</v>
       </c>
       <c r="K253" t="s">
         <v>2047</v>
@@ -28562,7 +28562,7 @@
         <v>1954</v>
       </c>
       <c r="J254" t="n">
-        <v>-1.91295368688773</v>
+        <v>-1.91295368688782</v>
       </c>
       <c r="K254" t="s">
         <v>2050</v>
@@ -28597,7 +28597,7 @@
         <v>1954</v>
       </c>
       <c r="J255" t="n">
-        <v>-1.91295368688773</v>
+        <v>-1.91295368688782</v>
       </c>
       <c r="K255" t="s">
         <v>2051</v>
@@ -28632,7 +28632,7 @@
         <v>1954</v>
       </c>
       <c r="J256" t="n">
-        <v>-1.91295368688773</v>
+        <v>-1.91295368688782</v>
       </c>
       <c r="K256" t="s">
         <v>2052</v>
@@ -28667,7 +28667,7 @@
         <v>1954</v>
       </c>
       <c r="J257" t="n">
-        <v>-1.91381221550479</v>
+        <v>-1.91381221550521</v>
       </c>
       <c r="K257" t="s">
         <v>2055</v>
@@ -28702,7 +28702,7 @@
         <v>1954</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.91381221550479</v>
+        <v>-1.91381221550521</v>
       </c>
       <c r="K258" t="s">
         <v>2056</v>
@@ -28737,7 +28737,7 @@
         <v>1954</v>
       </c>
       <c r="J259" t="n">
-        <v>-1.91381221550479</v>
+        <v>-1.91381221550521</v>
       </c>
       <c r="K259" t="s">
         <v>2057</v>
@@ -28772,7 +28772,7 @@
         <v>1954</v>
       </c>
       <c r="J260" t="n">
-        <v>-1.914252187758</v>
+        <v>-1.91425218775784</v>
       </c>
       <c r="K260" t="s">
         <v>2060</v>
@@ -28807,7 +28807,7 @@
         <v>1954</v>
       </c>
       <c r="J261" t="n">
-        <v>-1.914252187758</v>
+        <v>-1.91425218775784</v>
       </c>
       <c r="K261" t="s">
         <v>2061</v>
@@ -28842,7 +28842,7 @@
         <v>1954</v>
       </c>
       <c r="J262" t="n">
-        <v>-1.914252187758</v>
+        <v>-1.91425218775784</v>
       </c>
       <c r="K262" t="s">
         <v>2062</v>
@@ -28877,7 +28877,7 @@
         <v>1954</v>
       </c>
       <c r="J263" t="n">
-        <v>-1.95049121425186</v>
+        <v>-1.95049121425174</v>
       </c>
       <c r="K263" t="s">
         <v>2065</v>
@@ -28912,7 +28912,7 @@
         <v>1954</v>
       </c>
       <c r="J264" t="n">
-        <v>-1.95049121425186</v>
+        <v>-1.95049121425174</v>
       </c>
       <c r="K264" t="s">
         <v>2066</v>
@@ -28947,7 +28947,7 @@
         <v>1954</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.95049121425186</v>
+        <v>-1.95049121425174</v>
       </c>
       <c r="K265" t="s">
         <v>2067</v>
@@ -28982,7 +28982,7 @@
         <v>1954</v>
       </c>
       <c r="J266" t="n">
-        <v>-1.95736346189948</v>
+        <v>-1.95736346189967</v>
       </c>
       <c r="K266" t="s">
         <v>2070</v>
@@ -29017,7 +29017,7 @@
         <v>1954</v>
       </c>
       <c r="J267" t="n">
-        <v>-1.95736346189948</v>
+        <v>-1.95736346189967</v>
       </c>
       <c r="K267" t="s">
         <v>2071</v>
@@ -29052,7 +29052,7 @@
         <v>1954</v>
       </c>
       <c r="J268" t="n">
-        <v>-1.95736346189948</v>
+        <v>-1.95736346189967</v>
       </c>
       <c r="K268" t="s">
         <v>2072</v>
@@ -29087,7 +29087,7 @@
         <v>1954</v>
       </c>
       <c r="J269" t="n">
-        <v>-2.03516680261491</v>
+        <v>-2.03516680261468</v>
       </c>
       <c r="K269" t="s">
         <v>2073</v>
@@ -29122,7 +29122,7 @@
         <v>1954</v>
       </c>
       <c r="J270" t="n">
-        <v>-2.03516680261491</v>
+        <v>-2.03516680261468</v>
       </c>
       <c r="K270" t="s">
         <v>2074</v>
@@ -29157,7 +29157,7 @@
         <v>1954</v>
       </c>
       <c r="J271" t="n">
-        <v>-2.03516680261491</v>
+        <v>-2.03516680261468</v>
       </c>
       <c r="K271" t="s">
         <v>2075</v>
@@ -29192,7 +29192,7 @@
         <v>2077</v>
       </c>
       <c r="J272" t="n">
-        <v>2.35770303328905</v>
+        <v>2.35770303328862</v>
       </c>
       <c r="K272" t="s">
         <v>2078</v>
@@ -29227,7 +29227,7 @@
         <v>2077</v>
       </c>
       <c r="J273" t="n">
-        <v>2.35770303328905</v>
+        <v>2.35770303328862</v>
       </c>
       <c r="K273" t="s">
         <v>2079</v>
@@ -29262,7 +29262,7 @@
         <v>2077</v>
       </c>
       <c r="J274" t="n">
-        <v>2.35770303328905</v>
+        <v>2.35770303328862</v>
       </c>
       <c r="K274" t="s">
         <v>2080</v>
@@ -29297,7 +29297,7 @@
         <v>2077</v>
       </c>
       <c r="J275" t="n">
-        <v>2.14545375369688</v>
+        <v>2.14545375369625</v>
       </c>
       <c r="K275" t="s">
         <v>2081</v>
@@ -29332,7 +29332,7 @@
         <v>2077</v>
       </c>
       <c r="J276" t="n">
-        <v>2.14545375369688</v>
+        <v>2.14545375369625</v>
       </c>
       <c r="K276" t="s">
         <v>2082</v>
@@ -29367,7 +29367,7 @@
         <v>2077</v>
       </c>
       <c r="J277" t="n">
-        <v>2.14545375369688</v>
+        <v>2.14545375369625</v>
       </c>
       <c r="K277" t="s">
         <v>2083</v>
@@ -29402,7 +29402,7 @@
         <v>2077</v>
       </c>
       <c r="J278" t="n">
-        <v>2.08978537172296</v>
+        <v>2.08978537172267</v>
       </c>
       <c r="K278" t="s">
         <v>2086</v>
@@ -29437,7 +29437,7 @@
         <v>2077</v>
       </c>
       <c r="J279" t="n">
-        <v>2.08978537172296</v>
+        <v>2.08978537172267</v>
       </c>
       <c r="K279" t="s">
         <v>2087</v>
@@ -29472,7 +29472,7 @@
         <v>2077</v>
       </c>
       <c r="J280" t="n">
-        <v>2.08978537172296</v>
+        <v>2.08978537172267</v>
       </c>
       <c r="K280" t="s">
         <v>2088</v>
@@ -29507,7 +29507,7 @@
         <v>2077</v>
       </c>
       <c r="J281" t="n">
-        <v>1.94344716730673</v>
+        <v>1.94344716730664</v>
       </c>
       <c r="K281" t="s">
         <v>2091</v>
@@ -29542,7 +29542,7 @@
         <v>2077</v>
       </c>
       <c r="J282" t="n">
-        <v>1.94344716730673</v>
+        <v>1.94344716730664</v>
       </c>
       <c r="K282" t="s">
         <v>2092</v>
@@ -29577,7 +29577,7 @@
         <v>2077</v>
       </c>
       <c r="J283" t="n">
-        <v>1.94344716730673</v>
+        <v>1.94344716730664</v>
       </c>
       <c r="K283" t="s">
         <v>2093</v>
@@ -29612,7 +29612,7 @@
         <v>2077</v>
       </c>
       <c r="J284" t="n">
-        <v>1.91543781228779</v>
+        <v>1.91543781228765</v>
       </c>
       <c r="K284" t="s">
         <v>2094</v>
@@ -29647,7 +29647,7 @@
         <v>2077</v>
       </c>
       <c r="J285" t="n">
-        <v>1.91543781228779</v>
+        <v>1.91543781228765</v>
       </c>
       <c r="K285" t="s">
         <v>2095</v>
@@ -29682,7 +29682,7 @@
         <v>2077</v>
       </c>
       <c r="J286" t="n">
-        <v>1.91543781228779</v>
+        <v>1.91543781228765</v>
       </c>
       <c r="K286" t="s">
         <v>2096</v>
@@ -29717,7 +29717,7 @@
         <v>2077</v>
       </c>
       <c r="J287" t="n">
-        <v>1.7838114328817</v>
+        <v>1.78381143288193</v>
       </c>
       <c r="K287" t="s">
         <v>2099</v>
@@ -29752,7 +29752,7 @@
         <v>2077</v>
       </c>
       <c r="J288" t="n">
-        <v>1.7838114328817</v>
+        <v>1.78381143288193</v>
       </c>
       <c r="K288" t="s">
         <v>2100</v>
@@ -29787,7 +29787,7 @@
         <v>2077</v>
       </c>
       <c r="J289" t="n">
-        <v>1.7838114328817</v>
+        <v>1.78381143288193</v>
       </c>
       <c r="K289" t="s">
         <v>2101</v>
@@ -29822,7 +29822,7 @@
         <v>2077</v>
       </c>
       <c r="J290" t="n">
-        <v>1.72691289966202</v>
+        <v>1.72691289966172</v>
       </c>
       <c r="K290" t="s">
         <v>2104</v>
@@ -29857,7 +29857,7 @@
         <v>2077</v>
       </c>
       <c r="J291" t="n">
-        <v>1.72691289966202</v>
+        <v>1.72691289966172</v>
       </c>
       <c r="K291" t="s">
         <v>2105</v>
@@ -29892,7 +29892,7 @@
         <v>2077</v>
       </c>
       <c r="J292" t="n">
-        <v>1.72691289966202</v>
+        <v>1.72691289966172</v>
       </c>
       <c r="K292" t="s">
         <v>2106</v>
@@ -29927,7 +29927,7 @@
         <v>2077</v>
       </c>
       <c r="J293" t="n">
-        <v>1.69142484242852</v>
+        <v>1.69142484242815</v>
       </c>
       <c r="K293" t="s">
         <v>2109</v>
@@ -29962,7 +29962,7 @@
         <v>2077</v>
       </c>
       <c r="J294" t="n">
-        <v>1.69142484242852</v>
+        <v>1.69142484242815</v>
       </c>
       <c r="K294" t="s">
         <v>2110</v>
@@ -29997,7 +29997,7 @@
         <v>2077</v>
       </c>
       <c r="J295" t="n">
-        <v>1.69142484242852</v>
+        <v>1.69142484242815</v>
       </c>
       <c r="K295" t="s">
         <v>2111</v>
@@ -30032,7 +30032,7 @@
         <v>2077</v>
       </c>
       <c r="J296" t="n">
-        <v>-1.69712431360955</v>
+        <v>-1.69712431360973</v>
       </c>
       <c r="K296" t="s">
         <v>2114</v>
@@ -30067,7 +30067,7 @@
         <v>2077</v>
       </c>
       <c r="J297" t="n">
-        <v>-1.69712431360955</v>
+        <v>-1.69712431360973</v>
       </c>
       <c r="K297" t="s">
         <v>2115</v>
@@ -30102,7 +30102,7 @@
         <v>2077</v>
       </c>
       <c r="J298" t="n">
-        <v>-1.69712431360955</v>
+        <v>-1.69712431360973</v>
       </c>
       <c r="K298" t="s">
         <v>2116</v>
@@ -30137,7 +30137,7 @@
         <v>2077</v>
       </c>
       <c r="J299" t="n">
-        <v>-1.69779626755744</v>
+        <v>-1.69779626755763</v>
       </c>
       <c r="K299" t="s">
         <v>2119</v>
@@ -30172,7 +30172,7 @@
         <v>2077</v>
       </c>
       <c r="J300" t="n">
-        <v>-1.69779626755744</v>
+        <v>-1.69779626755763</v>
       </c>
       <c r="K300" t="s">
         <v>2120</v>
@@ -30207,7 +30207,7 @@
         <v>2077</v>
       </c>
       <c r="J301" t="n">
-        <v>-1.69779626755744</v>
+        <v>-1.69779626755763</v>
       </c>
       <c r="K301" t="s">
         <v>2121</v>
@@ -30242,7 +30242,7 @@
         <v>2077</v>
       </c>
       <c r="J302" t="n">
-        <v>-1.72125126165315</v>
+        <v>-1.72125126165323</v>
       </c>
       <c r="K302" t="s">
         <v>2124</v>
@@ -30277,7 +30277,7 @@
         <v>2077</v>
       </c>
       <c r="J303" t="n">
-        <v>-1.72125126165315</v>
+        <v>-1.72125126165323</v>
       </c>
       <c r="K303" t="s">
         <v>2125</v>
@@ -30312,7 +30312,7 @@
         <v>2077</v>
       </c>
       <c r="J304" t="n">
-        <v>-1.72125126165315</v>
+        <v>-1.72125126165323</v>
       </c>
       <c r="K304" t="s">
         <v>2126</v>
@@ -30347,7 +30347,7 @@
         <v>2077</v>
       </c>
       <c r="J305" t="n">
-        <v>-1.7223515843065</v>
+        <v>-1.72235158430665</v>
       </c>
       <c r="K305" t="s">
         <v>2129</v>
@@ -30382,7 +30382,7 @@
         <v>2077</v>
       </c>
       <c r="J306" t="n">
-        <v>-1.7223515843065</v>
+        <v>-1.72235158430665</v>
       </c>
       <c r="K306" t="s">
         <v>2130</v>
@@ -30417,7 +30417,7 @@
         <v>2077</v>
       </c>
       <c r="J307" t="n">
-        <v>-1.7223515843065</v>
+        <v>-1.72235158430665</v>
       </c>
       <c r="K307" t="s">
         <v>2131</v>
@@ -30452,7 +30452,7 @@
         <v>2077</v>
       </c>
       <c r="J308" t="n">
-        <v>-1.72475438155006</v>
+        <v>-1.72475438155025</v>
       </c>
       <c r="K308" t="s">
         <v>2134</v>
@@ -30487,7 +30487,7 @@
         <v>2077</v>
       </c>
       <c r="J309" t="n">
-        <v>-1.72475438155006</v>
+        <v>-1.72475438155025</v>
       </c>
       <c r="K309" t="s">
         <v>2135</v>
@@ -30522,7 +30522,7 @@
         <v>2077</v>
       </c>
       <c r="J310" t="n">
-        <v>-1.72475438155006</v>
+        <v>-1.72475438155025</v>
       </c>
       <c r="K310" t="s">
         <v>2136</v>
@@ -30557,7 +30557,7 @@
         <v>2077</v>
       </c>
       <c r="J311" t="n">
-        <v>-1.77168031782548</v>
+        <v>-1.77168031782568</v>
       </c>
       <c r="K311" t="s">
         <v>2137</v>
@@ -30592,7 +30592,7 @@
         <v>2077</v>
       </c>
       <c r="J312" t="n">
-        <v>-1.77168031782548</v>
+        <v>-1.77168031782568</v>
       </c>
       <c r="K312" t="s">
         <v>2138</v>
@@ -30627,7 +30627,7 @@
         <v>2077</v>
       </c>
       <c r="J313" t="n">
-        <v>-1.77168031782548</v>
+        <v>-1.77168031782568</v>
       </c>
       <c r="K313" t="s">
         <v>2139</v>
@@ -30662,7 +30662,7 @@
         <v>2077</v>
       </c>
       <c r="J314" t="n">
-        <v>-1.77514878715049</v>
+        <v>-1.77514878715078</v>
       </c>
       <c r="K314" t="s">
         <v>2142</v>
@@ -30697,7 +30697,7 @@
         <v>2077</v>
       </c>
       <c r="J315" t="n">
-        <v>-1.77514878715049</v>
+        <v>-1.77514878715078</v>
       </c>
       <c r="K315" t="s">
         <v>2143</v>
@@ -30732,7 +30732,7 @@
         <v>2077</v>
       </c>
       <c r="J316" t="n">
-        <v>-1.77514878715049</v>
+        <v>-1.77514878715078</v>
       </c>
       <c r="K316" t="s">
         <v>2144</v>
@@ -30767,7 +30767,7 @@
         <v>2077</v>
       </c>
       <c r="J317" t="n">
-        <v>-1.77972635095557</v>
+        <v>-1.77972635095574</v>
       </c>
       <c r="K317" t="s">
         <v>2147</v>
@@ -30802,7 +30802,7 @@
         <v>2077</v>
       </c>
       <c r="J318" t="n">
-        <v>-1.77972635095557</v>
+        <v>-1.77972635095574</v>
       </c>
       <c r="K318" t="s">
         <v>2148</v>
@@ -30837,7 +30837,7 @@
         <v>2077</v>
       </c>
       <c r="J319" t="n">
-        <v>-1.77972635095557</v>
+        <v>-1.77972635095574</v>
       </c>
       <c r="K319" t="s">
         <v>2149</v>
@@ -30872,7 +30872,7 @@
         <v>2077</v>
       </c>
       <c r="J320" t="n">
-        <v>-1.81371527408252</v>
+        <v>-1.8137152740828</v>
       </c>
       <c r="K320" t="s">
         <v>2150</v>
@@ -30907,7 +30907,7 @@
         <v>2077</v>
       </c>
       <c r="J321" t="n">
-        <v>-1.81371527408252</v>
+        <v>-1.8137152740828</v>
       </c>
       <c r="K321" t="s">
         <v>2151</v>
@@ -30942,7 +30942,7 @@
         <v>2077</v>
       </c>
       <c r="J322" t="n">
-        <v>-1.81371527408252</v>
+        <v>-1.8137152740828</v>
       </c>
       <c r="K322" t="s">
         <v>2152</v>
@@ -30977,7 +30977,7 @@
         <v>2077</v>
       </c>
       <c r="J323" t="n">
-        <v>-1.8177374450805</v>
+        <v>-1.81773744508097</v>
       </c>
       <c r="K323" t="s">
         <v>2155</v>
@@ -31012,7 +31012,7 @@
         <v>2077</v>
       </c>
       <c r="J324" t="n">
-        <v>-1.8177374450805</v>
+        <v>-1.81773744508097</v>
       </c>
       <c r="K324" t="s">
         <v>2156</v>
@@ -31047,7 +31047,7 @@
         <v>2077</v>
       </c>
       <c r="J325" t="n">
-        <v>-1.8177374450805</v>
+        <v>-1.81773744508097</v>
       </c>
       <c r="K325" t="s">
         <v>2157</v>
@@ -31082,7 +31082,7 @@
         <v>2077</v>
       </c>
       <c r="J326" t="n">
-        <v>-1.83261883083227</v>
+        <v>-1.8326188308325</v>
       </c>
       <c r="K326" t="s">
         <v>2160</v>
@@ -31117,7 +31117,7 @@
         <v>2077</v>
       </c>
       <c r="J327" t="n">
-        <v>-1.83261883083227</v>
+        <v>-1.8326188308325</v>
       </c>
       <c r="K327" t="s">
         <v>2161</v>
@@ -31152,7 +31152,7 @@
         <v>2077</v>
       </c>
       <c r="J328" t="n">
-        <v>-1.83261883083227</v>
+        <v>-1.8326188308325</v>
       </c>
       <c r="K328" t="s">
         <v>2162</v>
@@ -31187,7 +31187,7 @@
         <v>2077</v>
       </c>
       <c r="J329" t="n">
-        <v>-1.88217557114064</v>
+        <v>-1.88217557114074</v>
       </c>
       <c r="K329" t="s">
         <v>2165</v>
@@ -31222,7 +31222,7 @@
         <v>2077</v>
       </c>
       <c r="J330" t="n">
-        <v>-1.88217557114064</v>
+        <v>-1.88217557114074</v>
       </c>
       <c r="K330" t="s">
         <v>2166</v>
@@ -31257,7 +31257,7 @@
         <v>2077</v>
       </c>
       <c r="J331" t="n">
-        <v>-1.88217557114064</v>
+        <v>-1.88217557114074</v>
       </c>
       <c r="K331" t="s">
         <v>2167</v>
@@ -31292,7 +31292,7 @@
         <v>2077</v>
       </c>
       <c r="J332" t="n">
-        <v>-1.8916074010116</v>
+        <v>-1.8916074010119</v>
       </c>
       <c r="K332" t="s">
         <v>2170</v>
@@ -31327,7 +31327,7 @@
         <v>2077</v>
       </c>
       <c r="J333" t="n">
-        <v>-1.8916074010116</v>
+        <v>-1.8916074010119</v>
       </c>
       <c r="K333" t="s">
         <v>2171</v>
@@ -31362,7 +31362,7 @@
         <v>2077</v>
       </c>
       <c r="J334" t="n">
-        <v>-1.8916074010116</v>
+        <v>-1.8916074010119</v>
       </c>
       <c r="K334" t="s">
         <v>2172</v>
@@ -31397,7 +31397,7 @@
         <v>2077</v>
       </c>
       <c r="J335" t="n">
-        <v>-1.90705615672073</v>
+        <v>-1.90705615672098</v>
       </c>
       <c r="K335" t="s">
         <v>2175</v>
@@ -31432,7 +31432,7 @@
         <v>2077</v>
       </c>
       <c r="J336" t="n">
-        <v>-1.90705615672073</v>
+        <v>-1.90705615672098</v>
       </c>
       <c r="K336" t="s">
         <v>2176</v>
@@ -31467,7 +31467,7 @@
         <v>2077</v>
       </c>
       <c r="J337" t="n">
-        <v>-1.90705615672073</v>
+        <v>-1.90705615672098</v>
       </c>
       <c r="K337" t="s">
         <v>2177</v>
@@ -31502,7 +31502,7 @@
         <v>2077</v>
       </c>
       <c r="J338" t="n">
-        <v>-1.93576013996637</v>
+        <v>-1.93576013996659</v>
       </c>
       <c r="K338" t="s">
         <v>2178</v>
@@ -31537,7 +31537,7 @@
         <v>2077</v>
       </c>
       <c r="J339" t="n">
-        <v>-1.93576013996637</v>
+        <v>-1.93576013996659</v>
       </c>
       <c r="K339" t="s">
         <v>2179</v>
@@ -31572,7 +31572,7 @@
         <v>2077</v>
       </c>
       <c r="J340" t="n">
-        <v>-1.93576013996637</v>
+        <v>-1.93576013996659</v>
       </c>
       <c r="K340" t="s">
         <v>2180</v>
@@ -31607,7 +31607,7 @@
         <v>2077</v>
       </c>
       <c r="J341" t="n">
-        <v>-1.98625908977074</v>
+        <v>-1.98625908977098</v>
       </c>
       <c r="K341" t="s">
         <v>2183</v>
@@ -31642,7 +31642,7 @@
         <v>2077</v>
       </c>
       <c r="J342" t="n">
-        <v>-1.98625908977074</v>
+        <v>-1.98625908977098</v>
       </c>
       <c r="K342" t="s">
         <v>2184</v>
@@ -31677,7 +31677,7 @@
         <v>2077</v>
       </c>
       <c r="J343" t="n">
-        <v>-1.98625908977074</v>
+        <v>-1.98625908977098</v>
       </c>
       <c r="K343" t="s">
         <v>2185</v>
@@ -31712,7 +31712,7 @@
         <v>2077</v>
       </c>
       <c r="J344" t="n">
-        <v>-2.00017915846747</v>
+        <v>-2.00017915846768</v>
       </c>
       <c r="K344" t="s">
         <v>2187</v>
@@ -31747,7 +31747,7 @@
         <v>2077</v>
       </c>
       <c r="J345" t="n">
-        <v>-2.00017915846747</v>
+        <v>-2.00017915846768</v>
       </c>
       <c r="K345" t="s">
         <v>2188</v>
@@ -31782,7 +31782,7 @@
         <v>2077</v>
       </c>
       <c r="J346" t="n">
-        <v>-2.00017915846747</v>
+        <v>-2.00017915846768</v>
       </c>
       <c r="K346" t="s">
         <v>2189</v>
@@ -31817,7 +31817,7 @@
         <v>2077</v>
       </c>
       <c r="J347" t="n">
-        <v>-2.00418062847911</v>
+        <v>-2.00418062847958</v>
       </c>
       <c r="K347" t="s">
         <v>2190</v>
@@ -31852,7 +31852,7 @@
         <v>2077</v>
       </c>
       <c r="J348" t="n">
-        <v>-2.00418062847911</v>
+        <v>-2.00418062847958</v>
       </c>
       <c r="K348" t="s">
         <v>2191</v>
@@ -31887,7 +31887,7 @@
         <v>2077</v>
       </c>
       <c r="J349" t="n">
-        <v>-2.00418062847911</v>
+        <v>-2.00418062847958</v>
       </c>
       <c r="K349" t="s">
         <v>2192</v>
@@ -31922,7 +31922,7 @@
         <v>2077</v>
       </c>
       <c r="J350" t="n">
-        <v>-2.0072250915997</v>
+        <v>-2.00722509160032</v>
       </c>
       <c r="K350" t="s">
         <v>2195</v>
@@ -31957,7 +31957,7 @@
         <v>2077</v>
       </c>
       <c r="J351" t="n">
-        <v>-2.0072250915997</v>
+        <v>-2.00722509160032</v>
       </c>
       <c r="K351" t="s">
         <v>2196</v>
@@ -31992,7 +31992,7 @@
         <v>2077</v>
       </c>
       <c r="J352" t="n">
-        <v>-2.0072250915997</v>
+        <v>-2.00722509160032</v>
       </c>
       <c r="K352" t="s">
         <v>2197</v>
@@ -32027,7 +32027,7 @@
         <v>2077</v>
       </c>
       <c r="J353" t="n">
-        <v>-2.02176191168199</v>
+        <v>-2.0217619116824</v>
       </c>
       <c r="K353" t="s">
         <v>2200</v>
@@ -32062,7 +32062,7 @@
         <v>2077</v>
       </c>
       <c r="J354" t="n">
-        <v>-2.02176191168199</v>
+        <v>-2.0217619116824</v>
       </c>
       <c r="K354" t="s">
         <v>2201</v>
@@ -32097,7 +32097,7 @@
         <v>2077</v>
       </c>
       <c r="J355" t="n">
-        <v>-2.02176191168199</v>
+        <v>-2.0217619116824</v>
       </c>
       <c r="K355" t="s">
         <v>2202</v>
@@ -32132,7 +32132,7 @@
         <v>2077</v>
       </c>
       <c r="J356" t="n">
-        <v>-2.04513981236972</v>
+        <v>-2.04513981236997</v>
       </c>
       <c r="K356" t="s">
         <v>2205</v>
@@ -32167,7 +32167,7 @@
         <v>2077</v>
       </c>
       <c r="J357" t="n">
-        <v>-2.04513981236972</v>
+        <v>-2.04513981236997</v>
       </c>
       <c r="K357" t="s">
         <v>2206</v>
@@ -32202,7 +32202,7 @@
         <v>2077</v>
       </c>
       <c r="J358" t="n">
-        <v>-2.04513981236972</v>
+        <v>-2.04513981236997</v>
       </c>
       <c r="K358" t="s">
         <v>2207</v>
@@ -32237,7 +32237,7 @@
         <v>2077</v>
       </c>
       <c r="J359" t="n">
-        <v>-2.04801682840487</v>
+        <v>-2.04801682840505</v>
       </c>
       <c r="K359" t="s">
         <v>2210</v>
@@ -32272,7 +32272,7 @@
         <v>2077</v>
       </c>
       <c r="J360" t="n">
-        <v>-2.04801682840487</v>
+        <v>-2.04801682840505</v>
       </c>
       <c r="K360" t="s">
         <v>2211</v>
@@ -32307,7 +32307,7 @@
         <v>2077</v>
       </c>
       <c r="J361" t="n">
-        <v>-2.04801682840487</v>
+        <v>-2.04801682840505</v>
       </c>
       <c r="K361" t="s">
         <v>2212</v>
@@ -32342,7 +32342,7 @@
         <v>2077</v>
       </c>
       <c r="J362" t="n">
-        <v>-2.12872342665991</v>
+        <v>-2.12872342666033</v>
       </c>
       <c r="K362" t="s">
         <v>2213</v>
@@ -32377,7 +32377,7 @@
         <v>2077</v>
       </c>
       <c r="J363" t="n">
-        <v>-2.12872342665991</v>
+        <v>-2.12872342666033</v>
       </c>
       <c r="K363" t="s">
         <v>2214</v>
@@ -32412,7 +32412,7 @@
         <v>2077</v>
       </c>
       <c r="J364" t="n">
-        <v>-2.12872342665991</v>
+        <v>-2.12872342666033</v>
       </c>
       <c r="K364" t="s">
         <v>2215</v>
@@ -32447,7 +32447,7 @@
         <v>2077</v>
       </c>
       <c r="J365" t="n">
-        <v>-2.12955166678879</v>
+        <v>-2.12955166678928</v>
       </c>
       <c r="K365" t="s">
         <v>2218</v>
@@ -32482,7 +32482,7 @@
         <v>2077</v>
       </c>
       <c r="J366" t="n">
-        <v>-2.12955166678879</v>
+        <v>-2.12955166678928</v>
       </c>
       <c r="K366" t="s">
         <v>2219</v>
@@ -32517,7 +32517,7 @@
         <v>2077</v>
       </c>
       <c r="J367" t="n">
-        <v>-2.12955166678879</v>
+        <v>-2.12955166678928</v>
       </c>
       <c r="K367" t="s">
         <v>2220</v>
@@ -32552,7 +32552,7 @@
         <v>2077</v>
       </c>
       <c r="J368" t="n">
-        <v>-2.23036433872883</v>
+        <v>-2.23036433872922</v>
       </c>
       <c r="K368" t="s">
         <v>2223</v>
@@ -32587,7 +32587,7 @@
         <v>2077</v>
       </c>
       <c r="J369" t="n">
-        <v>-2.23036433872883</v>
+        <v>-2.23036433872922</v>
       </c>
       <c r="K369" t="s">
         <v>2224</v>
@@ -32622,7 +32622,7 @@
         <v>2077</v>
       </c>
       <c r="J370" t="n">
-        <v>-2.23036433872883</v>
+        <v>-2.23036433872922</v>
       </c>
       <c r="K370" t="s">
         <v>2225</v>
@@ -41574,25 +41574,25 @@
         <v>257</v>
       </c>
       <c r="D2" t="n">
-        <v>3.48412721247087</v>
+        <v>3.48412721247129</v>
       </c>
       <c r="E2" t="n">
-        <v>4.21161096897874</v>
+        <v>4.21161096897919</v>
       </c>
       <c r="F2" t="n">
-        <v>0.511141040596108</v>
+        <v>0.511141040596115</v>
       </c>
       <c r="G2" t="n">
         <v>0.556196949731639</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0287632004854827</v>
+        <v>0.0287632004854532</v>
       </c>
       <c r="I2" t="s">
         <v>258</v>
       </c>
       <c r="J2" t="n">
-        <v>4.21161096897874</v>
+        <v>4.21161096897919</v>
       </c>
       <c r="K2" t="s">
         <v>53</v>
@@ -41609,25 +41609,25 @@
         <v>257</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0579056109332</v>
+        <v>4.05790561093415</v>
       </c>
       <c r="E3" t="n">
-        <v>4.09186896159673</v>
+        <v>4.09186896159768</v>
       </c>
       <c r="F3" t="n">
-        <v>0.706915668807515</v>
+        <v>0.706915668807518</v>
       </c>
       <c r="G3" t="n">
         <v>0.64771515727271</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00213423371892398</v>
+        <v>0.00213423371891747</v>
       </c>
       <c r="I3" t="s">
         <v>258</v>
       </c>
       <c r="J3" t="n">
-        <v>4.09186896159673</v>
+        <v>4.09186896159768</v>
       </c>
       <c r="K3" t="s">
         <v>53</v>
@@ -41644,25 +41644,25 @@
         <v>259</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.48817220034216</v>
+        <v>-3.4881722003434</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.45429041055345</v>
+        <v>-3.45429041055465</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.764142564725145</v>
+        <v>-0.764142564725148</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.739464072659466</v>
+        <v>-0.739464072659462</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00480638078840438</v>
+        <v>0.00480638078838799</v>
       </c>
       <c r="I4" t="s">
         <v>260</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45429041055345</v>
+        <v>3.45429041055465</v>
       </c>
       <c r="K4" t="s">
         <v>77</v>
@@ -41679,10 +41679,10 @@
         <v>257</v>
       </c>
       <c r="D5" t="n">
-        <v>2.59704840828154</v>
+        <v>2.59704840828289</v>
       </c>
       <c r="E5" t="n">
-        <v>3.43072370614627</v>
+        <v>3.43072370614807</v>
       </c>
       <c r="F5" t="n">
         <v>1.10652955402938</v>
@@ -41691,13 +41691,13 @@
         <v>1.71883830144357</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00758883678463336</v>
+        <v>0.00758883678460189</v>
       </c>
       <c r="I5" t="s">
         <v>258</v>
       </c>
       <c r="J5" t="n">
-        <v>3.43072370614627</v>
+        <v>3.43072370614807</v>
       </c>
       <c r="K5" t="s">
         <v>53</v>
@@ -41714,25 +41714,25 @@
         <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.6431006226428</v>
+        <v>-4.64310062264231</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.91801758322992</v>
+        <v>-2.91801758322959</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.481424194198407</v>
+        <v>-0.481424194198411</v>
       </c>
       <c r="G6" t="n">
         <v>-0.309755822129894</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00523848038285669</v>
+        <v>0.00523848038285758</v>
       </c>
       <c r="I6" t="s">
         <v>260</v>
       </c>
       <c r="J6" t="n">
-        <v>2.91801758322992</v>
+        <v>2.91801758322959</v>
       </c>
       <c r="K6" t="s">
         <v>77</v>
@@ -41749,25 +41749,25 @@
         <v>257</v>
       </c>
       <c r="D7" t="n">
-        <v>3.7636806719603</v>
+        <v>3.76368067195992</v>
       </c>
       <c r="E7" t="n">
-        <v>2.88994882485898</v>
+        <v>2.88994882485869</v>
       </c>
       <c r="F7" t="n">
-        <v>0.390491085452169</v>
+        <v>0.390491085452172</v>
       </c>
       <c r="G7" t="n">
-        <v>0.30697306064274</v>
+        <v>0.306973060642743</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0458883291390167</v>
+        <v>0.0458883291390259</v>
       </c>
       <c r="I7" t="s">
         <v>258</v>
       </c>
       <c r="J7" t="n">
-        <v>2.88994882485898</v>
+        <v>2.88994882485869</v>
       </c>
       <c r="K7" t="s">
         <v>53</v>
@@ -41784,25 +41784,25 @@
         <v>257</v>
       </c>
       <c r="D8" t="n">
-        <v>4.63625010648508</v>
+        <v>4.6362501064832</v>
       </c>
       <c r="E8" t="n">
-        <v>2.88766399959336</v>
+        <v>2.88766399959219</v>
       </c>
       <c r="F8" t="n">
-        <v>0.43383159436647</v>
+        <v>0.433831594366477</v>
       </c>
       <c r="G8" t="n">
-        <v>0.253695986689166</v>
+        <v>0.25369598668917</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00936752333383787</v>
+        <v>0.00936752333385777</v>
       </c>
       <c r="I8" t="s">
         <v>258</v>
       </c>
       <c r="J8" t="n">
-        <v>2.88766399959336</v>
+        <v>2.88766399959219</v>
       </c>
       <c r="K8" t="s">
         <v>53</v>
@@ -41819,25 +41819,25 @@
         <v>257</v>
       </c>
       <c r="D9" t="n">
-        <v>5.39120431822785</v>
+        <v>5.39120431822591</v>
       </c>
       <c r="E9" t="n">
-        <v>2.75946428311049</v>
+        <v>2.75946428310965</v>
       </c>
       <c r="F9" t="n">
-        <v>0.473425956401499</v>
+        <v>0.473425956401492</v>
       </c>
       <c r="G9" t="n">
-        <v>0.248086314903823</v>
+        <v>0.248086314903833</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00154451475019221</v>
+        <v>0.00154451475019621</v>
       </c>
       <c r="I9" t="s">
         <v>258</v>
       </c>
       <c r="J9" t="n">
-        <v>2.75946428311049</v>
+        <v>2.75946428310965</v>
       </c>
       <c r="K9" t="s">
         <v>53</v>
@@ -41854,25 +41854,25 @@
         <v>259</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2056473247226</v>
+        <v>-3.20564732472382</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.70712786773349</v>
+        <v>-2.70712786773453</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.814653105627791</v>
+        <v>-0.814653105627787</v>
       </c>
       <c r="G10" t="n">
         <v>-0.693627278270892</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0066995036120439</v>
+        <v>0.006699503612022</v>
       </c>
       <c r="I10" t="s">
         <v>260</v>
       </c>
       <c r="J10" t="n">
-        <v>2.70712786773349</v>
+        <v>2.70712786773453</v>
       </c>
       <c r="K10" t="s">
         <v>77</v>
@@ -41889,25 +41889,25 @@
         <v>257</v>
       </c>
       <c r="D11" t="n">
-        <v>4.62111071584234</v>
+        <v>4.62111071584404</v>
       </c>
       <c r="E11" t="n">
-        <v>2.67928195405049</v>
+        <v>2.67928195405153</v>
       </c>
       <c r="F11" t="n">
         <v>1.11357792651978</v>
       </c>
       <c r="G11" t="n">
-        <v>0.661004499617025</v>
+        <v>0.661004499617036</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00000578698121715527</v>
+        <v>0.00000578698121710783</v>
       </c>
       <c r="I11" t="s">
         <v>258</v>
       </c>
       <c r="J11" t="n">
-        <v>2.67928195405049</v>
+        <v>2.67928195405153</v>
       </c>
       <c r="K11" t="s">
         <v>53</v>
@@ -41924,25 +41924,25 @@
         <v>259</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.91392784946407</v>
+        <v>-2.91392784946499</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.46744007167948</v>
+        <v>-2.46744007168027</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.608293578130187</v>
+        <v>-0.60829357813018</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.441667173414015</v>
+        <v>-0.441667173414011</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0423994348401228</v>
+        <v>0.0423994348400474</v>
       </c>
       <c r="I12" t="s">
         <v>260</v>
       </c>
       <c r="J12" t="n">
-        <v>2.46744007167948</v>
+        <v>2.46744007168027</v>
       </c>
       <c r="K12" t="s">
         <v>77</v>
@@ -41959,25 +41959,25 @@
         <v>257</v>
       </c>
       <c r="D13" t="n">
-        <v>3.56494917113547</v>
+        <v>3.56494917113622</v>
       </c>
       <c r="E13" t="n">
-        <v>2.43367358253488</v>
+        <v>2.43367358253536</v>
       </c>
       <c r="F13" t="n">
-        <v>0.538929847075671</v>
+        <v>0.538929847075678</v>
       </c>
       <c r="G13" t="n">
         <v>0.376663015654117</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0200502138751314</v>
+        <v>0.0200502138750984</v>
       </c>
       <c r="I13" t="s">
         <v>258</v>
       </c>
       <c r="J13" t="n">
-        <v>2.43367358253488</v>
+        <v>2.43367358253536</v>
       </c>
       <c r="K13" t="s">
         <v>53</v>
@@ -41994,25 +41994,25 @@
         <v>259</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.18249954175475</v>
+        <v>-4.18249954175594</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.37026507714375</v>
+        <v>-2.37026507714442</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.769667406399485</v>
+        <v>-0.769667406399481</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.431402455948792</v>
+        <v>-0.431402455948788</v>
       </c>
       <c r="H14" t="n">
-        <v>0.000803919817794644</v>
+        <v>0.00080391981779155</v>
       </c>
       <c r="I14" t="s">
         <v>260</v>
       </c>
       <c r="J14" t="n">
-        <v>2.37026507714375</v>
+        <v>2.37026507714442</v>
       </c>
       <c r="K14" t="s">
         <v>77</v>
@@ -42029,25 +42029,25 @@
         <v>257</v>
       </c>
       <c r="D15" t="n">
-        <v>3.25356019722794</v>
+        <v>3.25356019722925</v>
       </c>
       <c r="E15" t="n">
-        <v>2.32286999909538</v>
+        <v>2.32286999909631</v>
       </c>
       <c r="F15" t="n">
-        <v>0.900404254930402</v>
+        <v>0.900404254930407</v>
       </c>
       <c r="G15" t="n">
-        <v>0.413709003406986</v>
+        <v>0.413709003406987</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00466372750748004</v>
+        <v>0.00466372750746012</v>
       </c>
       <c r="I15" t="s">
         <v>258</v>
       </c>
       <c r="J15" t="n">
-        <v>2.32286999909538</v>
+        <v>2.32286999909631</v>
       </c>
       <c r="K15" t="s">
         <v>53</v>
@@ -42064,25 +42064,25 @@
         <v>257</v>
       </c>
       <c r="D16" t="n">
-        <v>4.01785730469829</v>
+        <v>4.0178573046977</v>
       </c>
       <c r="E16" t="n">
-        <v>2.29300875076236</v>
+        <v>2.29300875076201</v>
       </c>
       <c r="F16" t="n">
-        <v>0.402624473620964</v>
+        <v>0.402624473620968</v>
       </c>
       <c r="G16" t="n">
         <v>0.235246478227104</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0297225836246106</v>
+        <v>0.0297225836246233</v>
       </c>
       <c r="I16" t="s">
         <v>258</v>
       </c>
       <c r="J16" t="n">
-        <v>2.29300875076236</v>
+        <v>2.29300875076201</v>
       </c>
       <c r="K16" t="s">
         <v>53</v>
@@ -42099,25 +42099,25 @@
         <v>257</v>
       </c>
       <c r="D17" t="n">
-        <v>3.98464356645527</v>
+        <v>3.98464356645387</v>
       </c>
       <c r="E17" t="n">
-        <v>2.25856204382324</v>
+        <v>2.25856204382237</v>
       </c>
       <c r="F17" t="n">
         <v>0.349460320731534</v>
       </c>
       <c r="G17" t="n">
-        <v>0.202792633190107</v>
+        <v>0.2027926331901</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0491609257511754</v>
+        <v>0.0491609257512415</v>
       </c>
       <c r="I17" t="s">
         <v>258</v>
       </c>
       <c r="J17" t="n">
-        <v>2.25856204382324</v>
+        <v>2.25856204382237</v>
       </c>
       <c r="K17" t="s">
         <v>53</v>
@@ -42134,10 +42134,10 @@
         <v>257</v>
       </c>
       <c r="D18" t="n">
-        <v>3.73354463132412</v>
+        <v>3.73354463132545</v>
       </c>
       <c r="E18" t="n">
-        <v>2.139145025854</v>
+        <v>2.13914502585476</v>
       </c>
       <c r="F18" t="n">
         <v>0.776205944356491</v>
@@ -42146,13 +42146,13 @@
         <v>0.452181538535665</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00257723117457561</v>
+        <v>0.0025772311745655</v>
       </c>
       <c r="I18" t="s">
         <v>258</v>
       </c>
       <c r="J18" t="n">
-        <v>2.139145025854</v>
+        <v>2.13914502585476</v>
       </c>
       <c r="K18" t="s">
         <v>53</v>
@@ -42169,25 +42169,25 @@
         <v>257</v>
       </c>
       <c r="D19" t="n">
-        <v>3.90789142328785</v>
+        <v>3.9078914232885</v>
       </c>
       <c r="E19" t="n">
-        <v>2.02585547110767</v>
+        <v>2.02585547110802</v>
       </c>
       <c r="F19" t="n">
-        <v>0.611262057913592</v>
+        <v>0.611262057913596</v>
       </c>
       <c r="G19" t="n">
-        <v>0.285039023149753</v>
+        <v>0.285039023149757</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00639334703823942</v>
+        <v>0.00639334703822732</v>
       </c>
       <c r="I19" t="s">
         <v>258</v>
       </c>
       <c r="J19" t="n">
-        <v>2.02585547110767</v>
+        <v>2.02585547110802</v>
       </c>
       <c r="K19" t="s">
         <v>53</v>
@@ -42204,25 +42204,25 @@
         <v>257</v>
       </c>
       <c r="D20" t="n">
-        <v>4.63999909161652</v>
+        <v>4.63999909161819</v>
       </c>
       <c r="E20" t="n">
-        <v>1.95027028471379</v>
+        <v>1.95027028471445</v>
       </c>
       <c r="F20" t="n">
-        <v>1.01770635395491</v>
+        <v>1.01770635395492</v>
       </c>
       <c r="G20" t="n">
-        <v>0.437936508011411</v>
+        <v>0.437936508011408</v>
       </c>
       <c r="H20" t="n">
-        <v>0.000015255824033112</v>
+        <v>0.0000152558240329967</v>
       </c>
       <c r="I20" t="s">
         <v>258</v>
       </c>
       <c r="J20" t="n">
-        <v>1.95027028471379</v>
+        <v>1.95027028471445</v>
       </c>
       <c r="K20" t="s">
         <v>53</v>
@@ -42239,25 +42239,25 @@
         <v>257</v>
       </c>
       <c r="D21" t="n">
-        <v>4.98144460589408</v>
+        <v>4.98144460589381</v>
       </c>
       <c r="E21" t="n">
-        <v>1.94065606360804</v>
+        <v>1.94065606360796</v>
       </c>
       <c r="F21" t="n">
-        <v>0.540644965102562</v>
+        <v>0.540644965102565</v>
       </c>
       <c r="G21" t="n">
-        <v>0.215633974661486</v>
+        <v>0.21563397466149</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0014107092744139</v>
+        <v>0.00141070927441336</v>
       </c>
       <c r="I21" t="s">
         <v>258</v>
       </c>
       <c r="J21" t="n">
-        <v>1.94065606360804</v>
+        <v>1.94065606360796</v>
       </c>
       <c r="K21" t="s">
         <v>53</v>
@@ -46837,10 +46837,10 @@
         <v>258</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0021003423655932</v>
+        <v>0.00230604377551292</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0017281042968235</v>
+        <v>0.00166592856668802</v>
       </c>
       <c r="F2" t="s">
         <v>258</v>
@@ -46849,7 +46849,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.261638459436392</v>
+        <v>0.261923087947808</v>
       </c>
     </row>
     <row r="3">
@@ -46863,10 +46863,10 @@
         <v>260</v>
       </c>
       <c r="D3" t="n">
-        <v>0.295948403950462</v>
+        <v>0.289940138745485</v>
       </c>
       <c r="E3" t="n">
-        <v>0.283897559242273</v>
+        <v>0.279614121765403</v>
       </c>
       <c r="F3" t="s">
         <v>260</v>
@@ -46875,7 +46875,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.261638459436392</v>
+        <v>0.261923087947808</v>
       </c>
     </row>
   </sheetData>
@@ -46936,10 +46936,10 @@
         <v>257</v>
       </c>
       <c r="D2" t="n">
-        <v>3.73354463132412</v>
+        <v>3.73354463132545</v>
       </c>
       <c r="E2" t="n">
-        <v>2.139145025854</v>
+        <v>2.13914502585476</v>
       </c>
       <c r="F2" t="n">
         <v>0.776205944356491</v>
@@ -46948,7 +46948,7 @@
         <v>0.452181538535665</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00257723117457561</v>
+        <v>0.0025772311745655</v>
       </c>
     </row>
     <row r="3">
@@ -46962,19 +46962,19 @@
         <v>257</v>
       </c>
       <c r="D3" t="n">
-        <v>3.86009263449889</v>
+        <v>3.86009263449982</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6753015745171</v>
+        <v>1.67530157451752</v>
       </c>
       <c r="F3" t="n">
-        <v>0.623521234202403</v>
+        <v>0.623521234202407</v>
       </c>
       <c r="G3" t="n">
-        <v>0.277050076686802</v>
+        <v>0.277050076686805</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00599212463939542</v>
+        <v>0.00599212463938103</v>
       </c>
     </row>
     <row r="4">
@@ -46988,19 +46988,19 @@
         <v>257</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7636806719603</v>
+        <v>3.76368067195992</v>
       </c>
       <c r="E4" t="n">
-        <v>2.88994882485898</v>
+        <v>2.88994882485869</v>
       </c>
       <c r="F4" t="n">
-        <v>0.390491085452169</v>
+        <v>0.390491085452172</v>
       </c>
       <c r="G4" t="n">
-        <v>0.30697306064274</v>
+        <v>0.306973060642743</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0458883291390167</v>
+        <v>0.0458883291390259</v>
       </c>
     </row>
     <row r="5">
@@ -47014,19 +47014,19 @@
         <v>257</v>
       </c>
       <c r="D5" t="n">
-        <v>4.98144460589408</v>
+        <v>4.98144460589381</v>
       </c>
       <c r="E5" t="n">
-        <v>1.94065606360804</v>
+        <v>1.94065606360796</v>
       </c>
       <c r="F5" t="n">
-        <v>0.540644965102562</v>
+        <v>0.540644965102565</v>
       </c>
       <c r="G5" t="n">
-        <v>0.215633974661486</v>
+        <v>0.21563397466149</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0014107092744139</v>
+        <v>0.00141070927441336</v>
       </c>
     </row>
     <row r="6">
@@ -47040,19 +47040,19 @@
         <v>257</v>
       </c>
       <c r="D6" t="n">
-        <v>2.73482625328784</v>
+        <v>2.73482625328887</v>
       </c>
       <c r="E6" t="n">
-        <v>0.689942923559814</v>
+        <v>0.68994292356007</v>
       </c>
       <c r="F6" t="n">
-        <v>0.734899316084405</v>
+        <v>0.734899316084409</v>
       </c>
       <c r="G6" t="n">
         <v>0.124513552831967</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0309404458166754</v>
+        <v>0.0309404458166047</v>
       </c>
     </row>
     <row r="7">
@@ -47066,19 +47066,19 @@
         <v>257</v>
       </c>
       <c r="D7" t="n">
-        <v>3.48412721247087</v>
+        <v>3.48412721247129</v>
       </c>
       <c r="E7" t="n">
-        <v>4.21161096897874</v>
+        <v>4.21161096897919</v>
       </c>
       <c r="F7" t="n">
-        <v>0.511141040596108</v>
+        <v>0.511141040596115</v>
       </c>
       <c r="G7" t="n">
         <v>0.556196949731639</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0287632004854827</v>
+        <v>0.0287632004854532</v>
       </c>
     </row>
     <row r="8">
@@ -47092,19 +47092,19 @@
         <v>257</v>
       </c>
       <c r="D8" t="n">
-        <v>3.02232619597803</v>
+        <v>3.02232619597897</v>
       </c>
       <c r="E8" t="n">
-        <v>1.21762342907212</v>
+        <v>1.21762342907245</v>
       </c>
       <c r="F8" t="n">
-        <v>0.57798758632547</v>
+        <v>0.577987586325474</v>
       </c>
       <c r="G8" t="n">
-        <v>0.238397627244538</v>
+        <v>0.238397627244531</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0389508770244401</v>
+        <v>0.038950877024371</v>
       </c>
     </row>
     <row r="9">
@@ -47118,19 +47118,19 @@
         <v>257</v>
       </c>
       <c r="D9" t="n">
-        <v>3.56494917113547</v>
+        <v>3.56494917113622</v>
       </c>
       <c r="E9" t="n">
-        <v>2.43367358253488</v>
+        <v>2.43367358253536</v>
       </c>
       <c r="F9" t="n">
-        <v>0.538929847075671</v>
+        <v>0.538929847075678</v>
       </c>
       <c r="G9" t="n">
         <v>0.376663015654117</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0200502138751314</v>
+        <v>0.0200502138750984</v>
       </c>
     </row>
     <row r="10">
@@ -47144,19 +47144,19 @@
         <v>257</v>
       </c>
       <c r="D10" t="n">
-        <v>3.73743813462865</v>
+        <v>3.73743813463026</v>
       </c>
       <c r="E10" t="n">
-        <v>1.70746609331427</v>
+        <v>1.70746609331499</v>
       </c>
       <c r="F10" t="n">
         <v>1.17555954192002</v>
       </c>
       <c r="G10" t="n">
-        <v>0.53228062574421</v>
+        <v>0.532280625744207</v>
       </c>
       <c r="H10" t="n">
-        <v>0.000106229151131212</v>
+        <v>0.000106229151130476</v>
       </c>
     </row>
     <row r="11">
@@ -47170,10 +47170,10 @@
         <v>257</v>
       </c>
       <c r="D11" t="n">
-        <v>3.8513441467206</v>
+        <v>3.85134414672195</v>
       </c>
       <c r="E11" t="n">
-        <v>0.542911842457043</v>
+        <v>0.542911842457234</v>
       </c>
       <c r="F11" t="n">
         <v>0.856069503019839</v>
@@ -47182,7 +47182,7 @@
         <v>0.123548583319447</v>
       </c>
       <c r="H11" t="n">
-        <v>0.000910793906064538</v>
+        <v>0.000910793906060483</v>
       </c>
     </row>
     <row r="12">
@@ -47196,19 +47196,19 @@
         <v>257</v>
       </c>
       <c r="D12" t="n">
-        <v>3.43653976400488</v>
+        <v>3.43653976400594</v>
       </c>
       <c r="E12" t="n">
-        <v>1.02680366676304</v>
+        <v>1.02680366676339</v>
       </c>
       <c r="F12" t="n">
-        <v>0.641686249478891</v>
+        <v>0.641686249478894</v>
       </c>
       <c r="G12" t="n">
-        <v>0.196486754254998</v>
+        <v>0.196486754255005</v>
       </c>
       <c r="H12" t="n">
-        <v>0.012449682833929</v>
+        <v>0.0124496828338984</v>
       </c>
     </row>
     <row r="13">
@@ -47222,19 +47222,19 @@
         <v>257</v>
       </c>
       <c r="D13" t="n">
-        <v>4.01785730469829</v>
+        <v>4.0178573046977</v>
       </c>
       <c r="E13" t="n">
-        <v>2.29300875076236</v>
+        <v>2.29300875076201</v>
       </c>
       <c r="F13" t="n">
-        <v>0.402624473620964</v>
+        <v>0.402624473620968</v>
       </c>
       <c r="G13" t="n">
         <v>0.235246478227104</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0297225836246106</v>
+        <v>0.0297225836246233</v>
       </c>
     </row>
     <row r="14">
@@ -47248,19 +47248,19 @@
         <v>257</v>
       </c>
       <c r="D14" t="n">
-        <v>3.98464356645527</v>
+        <v>3.98464356645387</v>
       </c>
       <c r="E14" t="n">
-        <v>2.25856204382324</v>
+        <v>2.25856204382237</v>
       </c>
       <c r="F14" t="n">
         <v>0.349460320731534</v>
       </c>
       <c r="G14" t="n">
-        <v>0.202792633190107</v>
+        <v>0.2027926331901</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0491609257511754</v>
+        <v>0.0491609257512415</v>
       </c>
     </row>
     <row r="15">
@@ -47274,19 +47274,19 @@
         <v>257</v>
       </c>
       <c r="D15" t="n">
-        <v>5.39120431822785</v>
+        <v>5.39120431822591</v>
       </c>
       <c r="E15" t="n">
-        <v>2.75946428311049</v>
+        <v>2.75946428310965</v>
       </c>
       <c r="F15" t="n">
-        <v>0.473425956401499</v>
+        <v>0.473425956401492</v>
       </c>
       <c r="G15" t="n">
-        <v>0.248086314903823</v>
+        <v>0.248086314903833</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00154451475019221</v>
+        <v>0.00154451475019621</v>
       </c>
     </row>
     <row r="16">
@@ -47300,19 +47300,19 @@
         <v>257</v>
       </c>
       <c r="D16" t="n">
-        <v>4.63999909161652</v>
+        <v>4.63999909161819</v>
       </c>
       <c r="E16" t="n">
-        <v>1.95027028471379</v>
+        <v>1.95027028471445</v>
       </c>
       <c r="F16" t="n">
-        <v>1.01770635395491</v>
+        <v>1.01770635395492</v>
       </c>
       <c r="G16" t="n">
-        <v>0.437936508011411</v>
+        <v>0.437936508011408</v>
       </c>
       <c r="H16" t="n">
-        <v>0.000015255824033112</v>
+        <v>0.0000152558240329967</v>
       </c>
     </row>
     <row r="17">
@@ -47326,19 +47326,19 @@
         <v>257</v>
       </c>
       <c r="D17" t="n">
-        <v>3.45582833859613</v>
+        <v>3.45582833859568</v>
       </c>
       <c r="E17" t="n">
-        <v>1.38080190926919</v>
+        <v>1.38080190926899</v>
       </c>
       <c r="F17" t="n">
-        <v>0.443229914771752</v>
+        <v>0.443229914771749</v>
       </c>
       <c r="G17" t="n">
-        <v>0.153251367095777</v>
+        <v>0.153251367095773</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0493595637095691</v>
+        <v>0.0493595637095836</v>
       </c>
     </row>
     <row r="18">
@@ -47352,19 +47352,19 @@
         <v>257</v>
       </c>
       <c r="D18" t="n">
-        <v>5.38906401894189</v>
+        <v>5.38906401894094</v>
       </c>
       <c r="E18" t="n">
-        <v>1.54122114550377</v>
+        <v>1.54122114550348</v>
       </c>
       <c r="F18" t="n">
-        <v>0.52632796119514</v>
+        <v>0.526327961195147</v>
       </c>
       <c r="G18" t="n">
         <v>0.154106094959705</v>
       </c>
       <c r="H18" t="n">
-        <v>0.000752509639128927</v>
+        <v>0.000752509639129444</v>
       </c>
     </row>
     <row r="19">
@@ -47378,19 +47378,19 @@
         <v>257</v>
       </c>
       <c r="D19" t="n">
-        <v>4.78485577876723</v>
+        <v>4.78485577876909</v>
       </c>
       <c r="E19" t="n">
-        <v>1.61984583142134</v>
+        <v>1.61984583142196</v>
       </c>
       <c r="F19" t="n">
         <v>1.21030444088737</v>
       </c>
       <c r="G19" t="n">
-        <v>0.406216894205315</v>
+        <v>0.406216894205311</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00000105511858906761</v>
+        <v>0.00000105511858905703</v>
       </c>
     </row>
     <row r="20">
@@ -47404,19 +47404,19 @@
         <v>257</v>
       </c>
       <c r="D20" t="n">
-        <v>3.53239737620272</v>
+        <v>3.53239737620346</v>
       </c>
       <c r="E20" t="n">
-        <v>1.25070675325407</v>
+        <v>1.25070675325449</v>
       </c>
       <c r="F20" t="n">
-        <v>0.548678453178901</v>
+        <v>0.548678453178905</v>
       </c>
       <c r="G20" t="n">
-        <v>0.192139734440623</v>
+        <v>0.192139734440648</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0199697785749423</v>
+        <v>0.01996977857491</v>
       </c>
     </row>
     <row r="21">
@@ -47430,19 +47430,19 @@
         <v>257</v>
       </c>
       <c r="D21" t="n">
-        <v>4.6556107942551</v>
+        <v>4.65561079425315</v>
       </c>
       <c r="E21" t="n">
-        <v>1.93643849631223</v>
+        <v>1.93643849631136</v>
       </c>
       <c r="F21" t="n">
-        <v>0.390288027305772</v>
+        <v>0.390288027305775</v>
       </c>
       <c r="G21" t="n">
-        <v>0.166197324133869</v>
+        <v>0.166197324133865</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0139109266997039</v>
+        <v>0.0139109266997341</v>
       </c>
     </row>
     <row r="22">
@@ -47456,19 +47456,19 @@
         <v>257</v>
       </c>
       <c r="D22" t="n">
-        <v>3.55133054963881</v>
+        <v>3.55133054963986</v>
       </c>
       <c r="E22" t="n">
-        <v>0.361981137044834</v>
+        <v>0.361981137044957</v>
       </c>
       <c r="F22" t="n">
-        <v>0.65023547577804</v>
+        <v>0.650235475778043</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0678542820564978</v>
+        <v>0.0678542820565013</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00919586578193914</v>
+        <v>0.00919586578191578</v>
       </c>
     </row>
     <row r="23">
@@ -47482,10 +47482,10 @@
         <v>257</v>
       </c>
       <c r="D23" t="n">
-        <v>2.65974893423154</v>
+        <v>2.6597489342339</v>
       </c>
       <c r="E23" t="n">
-        <v>1.6924839816906</v>
+        <v>1.6924839816921</v>
       </c>
       <c r="F23" t="n">
         <v>0.908052221317053</v>
@@ -47494,7 +47494,7 @@
         <v>0.814536352968915</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0207062578721806</v>
+        <v>0.0207062578720566</v>
       </c>
     </row>
     <row r="24">
@@ -47508,19 +47508,19 @@
         <v>257</v>
       </c>
       <c r="D24" t="n">
-        <v>3.75592172911646</v>
+        <v>3.75592172911667</v>
       </c>
       <c r="E24" t="n">
-        <v>1.56752557905714</v>
+        <v>1.5675255790572</v>
       </c>
       <c r="F24" t="n">
-        <v>0.45217211778154</v>
+        <v>0.452172117781547</v>
       </c>
       <c r="G24" t="n">
         <v>0.193202899175844</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0285273198990564</v>
+        <v>0.0285273198990373</v>
       </c>
     </row>
     <row r="25">
@@ -47534,19 +47534,19 @@
         <v>257</v>
       </c>
       <c r="D25" t="n">
-        <v>4.98185666089365</v>
+        <v>4.98185666089281</v>
       </c>
       <c r="E25" t="n">
-        <v>1.9175060807997</v>
+        <v>1.91750608079927</v>
       </c>
       <c r="F25" t="n">
-        <v>0.493913465742601</v>
+        <v>0.493913465742612</v>
       </c>
       <c r="G25" t="n">
-        <v>0.191671175745434</v>
+        <v>0.191671175745427</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0025206308535614</v>
+        <v>0.0025206308535628</v>
       </c>
     </row>
     <row r="26">
@@ -47560,19 +47560,19 @@
         <v>257</v>
       </c>
       <c r="D26" t="n">
-        <v>4.63625010648508</v>
+        <v>4.6362501064832</v>
       </c>
       <c r="E26" t="n">
-        <v>2.88766399959336</v>
+        <v>2.88766399959219</v>
       </c>
       <c r="F26" t="n">
-        <v>0.43383159436647</v>
+        <v>0.433831594366477</v>
       </c>
       <c r="G26" t="n">
-        <v>0.253695986689166</v>
+        <v>0.25369598668917</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00936752333383787</v>
+        <v>0.00936752333385777</v>
       </c>
     </row>
     <row r="27">
@@ -47586,19 +47586,19 @@
         <v>257</v>
       </c>
       <c r="D27" t="n">
-        <v>4.47695446757125</v>
+        <v>4.47695446756939</v>
       </c>
       <c r="E27" t="n">
-        <v>1.35528443831667</v>
+        <v>1.35528443831608</v>
       </c>
       <c r="F27" t="n">
-        <v>0.373734813831231</v>
+        <v>0.373734813831238</v>
       </c>
       <c r="G27" t="n">
         <v>0.115830541313382</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0211577275099732</v>
+        <v>0.0211577275100143</v>
       </c>
     </row>
     <row r="28">
@@ -47612,10 +47612,10 @@
         <v>257</v>
       </c>
       <c r="D28" t="n">
-        <v>2.59704840828154</v>
+        <v>2.59704840828289</v>
       </c>
       <c r="E28" t="n">
-        <v>3.43072370614627</v>
+        <v>3.43072370614807</v>
       </c>
       <c r="F28" t="n">
         <v>1.10652955402938</v>
@@ -47624,7 +47624,7 @@
         <v>1.71883830144357</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00758883678463336</v>
+        <v>0.00758883678460189</v>
       </c>
     </row>
     <row r="29">
@@ -47638,19 +47638,19 @@
         <v>257</v>
       </c>
       <c r="D29" t="n">
-        <v>4.36923583625357</v>
+        <v>4.36923583625174</v>
       </c>
       <c r="E29" t="n">
-        <v>1.04109801403517</v>
+        <v>1.04109801403476</v>
       </c>
       <c r="F29" t="n">
-        <v>0.364190266189773</v>
+        <v>0.36419026618978</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0888436151185346</v>
+        <v>0.0888436151185381</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0268004621542109</v>
+        <v>0.0268004621542607</v>
       </c>
     </row>
     <row r="30">
@@ -47664,10 +47664,10 @@
         <v>257</v>
       </c>
       <c r="D30" t="n">
-        <v>5.35902883678282</v>
+        <v>5.35902883677954</v>
       </c>
       <c r="E30" t="n">
-        <v>1.52792157909879</v>
+        <v>1.52792157909785</v>
       </c>
       <c r="F30" t="n">
         <v>0.408929462160131</v>
@@ -47676,7 +47676,7 @@
         <v>0.119364485062864</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00392096600766495</v>
+        <v>0.00392096600768155</v>
       </c>
     </row>
     <row r="31">
@@ -47690,19 +47690,19 @@
         <v>257</v>
       </c>
       <c r="D31" t="n">
-        <v>4.0579056109332</v>
+        <v>4.05790561093415</v>
       </c>
       <c r="E31" t="n">
-        <v>4.09186896159673</v>
+        <v>4.09186896159768</v>
       </c>
       <c r="F31" t="n">
-        <v>0.706915668807515</v>
+        <v>0.706915668807518</v>
       </c>
       <c r="G31" t="n">
         <v>0.64771515727271</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00213423371892398</v>
+        <v>0.00213423371891747</v>
       </c>
     </row>
     <row r="32">
@@ -47716,19 +47716,19 @@
         <v>257</v>
       </c>
       <c r="D32" t="n">
-        <v>4.3751327426551</v>
+        <v>4.3751327426508</v>
       </c>
       <c r="E32" t="n">
-        <v>1.62989269211733</v>
+        <v>1.6298926921158</v>
       </c>
       <c r="F32" t="n">
-        <v>0.41570756647247</v>
+        <v>0.415707566472477</v>
       </c>
       <c r="G32" t="n">
-        <v>0.118876346227673</v>
+        <v>0.11887634622768</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0181780977415067</v>
+        <v>0.0181780977415992</v>
       </c>
     </row>
     <row r="33">
@@ -47742,19 +47742,19 @@
         <v>257</v>
       </c>
       <c r="D33" t="n">
-        <v>4.62111071584234</v>
+        <v>4.62111071584404</v>
       </c>
       <c r="E33" t="n">
-        <v>2.67928195405049</v>
+        <v>2.67928195405153</v>
       </c>
       <c r="F33" t="n">
         <v>1.11357792651978</v>
       </c>
       <c r="G33" t="n">
-        <v>0.661004499617025</v>
+        <v>0.661004499617036</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00000578698121715527</v>
+        <v>0.00000578698121710783</v>
       </c>
     </row>
     <row r="34">
@@ -47768,19 +47768,19 @@
         <v>257</v>
       </c>
       <c r="D34" t="n">
-        <v>3.38602785318051</v>
+        <v>3.38602785318104</v>
       </c>
       <c r="E34" t="n">
-        <v>1.66793812046201</v>
+        <v>1.66793812046226</v>
       </c>
       <c r="F34" t="n">
-        <v>0.475954518117916</v>
+        <v>0.47595451811792</v>
       </c>
       <c r="G34" t="n">
         <v>0.236382477562067</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0414404447556231</v>
+        <v>0.0414404447555803</v>
       </c>
     </row>
     <row r="35">
@@ -47794,19 +47794,19 @@
         <v>257</v>
       </c>
       <c r="D35" t="n">
-        <v>3.25356019722794</v>
+        <v>3.25356019722925</v>
       </c>
       <c r="E35" t="n">
-        <v>2.32286999909538</v>
+        <v>2.32286999909631</v>
       </c>
       <c r="F35" t="n">
-        <v>0.900404254930402</v>
+        <v>0.900404254930407</v>
       </c>
       <c r="G35" t="n">
-        <v>0.413709003406986</v>
+        <v>0.413709003406987</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00466372750748004</v>
+        <v>0.00466372750746012</v>
       </c>
     </row>
     <row r="36">
@@ -47820,10 +47820,10 @@
         <v>257</v>
       </c>
       <c r="D36" t="n">
-        <v>4.7454657404151</v>
+        <v>4.74546574041554</v>
       </c>
       <c r="E36" t="n">
-        <v>0.937464908130126</v>
+        <v>0.937464908130212</v>
       </c>
       <c r="F36" t="n">
         <v>0.608214456802912</v>
@@ -47832,7 +47832,7 @@
         <v>0.123011205118758</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0010496217954709</v>
+        <v>0.00104962179546898</v>
       </c>
     </row>
     <row r="37">
@@ -47846,19 +47846,19 @@
         <v>257</v>
       </c>
       <c r="D37" t="n">
-        <v>3.43733050053339</v>
+        <v>3.4373305005339</v>
       </c>
       <c r="E37" t="n">
-        <v>1.46365279679469</v>
+        <v>1.46365279679487</v>
       </c>
       <c r="F37" t="n">
-        <v>0.46075697068105</v>
+        <v>0.460756970681061</v>
       </c>
       <c r="G37" t="n">
         <v>0.20086323200114</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0424900636425741</v>
+        <v>0.0424900636425301</v>
       </c>
     </row>
     <row r="38">
@@ -47872,19 +47872,19 @@
         <v>257</v>
       </c>
       <c r="D38" t="n">
-        <v>3.90789142328785</v>
+        <v>3.9078914232885</v>
       </c>
       <c r="E38" t="n">
-        <v>2.02585547110767</v>
+        <v>2.02585547110802</v>
       </c>
       <c r="F38" t="n">
-        <v>0.611262057913592</v>
+        <v>0.611262057913596</v>
       </c>
       <c r="G38" t="n">
-        <v>0.285039023149753</v>
+        <v>0.285039023149757</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00639334703823942</v>
+        <v>0.00639334703822732</v>
       </c>
     </row>
     <row r="39">
@@ -47898,19 +47898,19 @@
         <v>257</v>
       </c>
       <c r="D39" t="n">
-        <v>3.52416544108985</v>
+        <v>3.5241654410901</v>
       </c>
       <c r="E39" t="n">
-        <v>0.351315283871953</v>
+        <v>0.351315283872003</v>
       </c>
       <c r="F39" t="n">
-        <v>0.442544837586855</v>
+        <v>0.442544837586858</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0444793521549478</v>
+        <v>0.0444793521549514</v>
       </c>
       <c r="H39" t="n">
-        <v>0.042879325715235</v>
+        <v>0.0428793257152083</v>
       </c>
     </row>
     <row r="40">
@@ -47924,19 +47924,19 @@
         <v>257</v>
       </c>
       <c r="D40" t="n">
-        <v>4.54124347346133</v>
+        <v>4.54124347346171</v>
       </c>
       <c r="E40" t="n">
-        <v>0.790370250291146</v>
+        <v>0.790370250291239</v>
       </c>
       <c r="F40" t="n">
         <v>0.637858174212326</v>
       </c>
       <c r="G40" t="n">
-        <v>0.103085503102417</v>
+        <v>0.10308550310242</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00132813918948552</v>
+        <v>0.00132813918948312</v>
       </c>
     </row>
     <row r="41">
@@ -47950,19 +47950,19 @@
         <v>259</v>
       </c>
       <c r="D41" t="n">
-        <v>-3.64623693732058</v>
+        <v>-3.64623693732049</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.3199014020049</v>
+        <v>-1.31990140200483</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.406638239570736</v>
+        <v>-0.406638239570739</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.150701153803702</v>
+        <v>-0.150701153803698</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0471262646478739</v>
+        <v>0.0471262646478661</v>
       </c>
     </row>
     <row r="42">
@@ -47976,19 +47976,19 @@
         <v>259</v>
       </c>
       <c r="D42" t="n">
-        <v>-3.85677969166516</v>
+        <v>-3.85677969166595</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.579125136815893</v>
+        <v>-0.57912513681602</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.600823364341839</v>
+        <v>-0.600823364341831</v>
       </c>
       <c r="G42" t="n">
         <v>-0.0923647276358395</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00726659536554964</v>
+        <v>0.00726659536553543</v>
       </c>
     </row>
     <row r="43">
@@ -48002,19 +48002,19 @@
         <v>259</v>
       </c>
       <c r="D43" t="n">
-        <v>-3.2056473247226</v>
+        <v>-3.20564732472382</v>
       </c>
       <c r="E43" t="n">
-        <v>-2.70712786773349</v>
+        <v>-2.70712786773453</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.814653105627791</v>
+        <v>-0.814653105627787</v>
       </c>
       <c r="G43" t="n">
         <v>-0.693627278270892</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0066995036120439</v>
+        <v>0.006699503612022</v>
       </c>
     </row>
     <row r="44">
@@ -48028,19 +48028,19 @@
         <v>259</v>
       </c>
       <c r="D44" t="n">
-        <v>-3.1900357062683</v>
+        <v>-3.19003570626898</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.471104874581622</v>
+        <v>-0.471104874581703</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.527188833099068</v>
+        <v>-0.527188833099064</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.0730972223111586</v>
+        <v>-0.073097222311155</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0407717901491273</v>
+        <v>0.0407717901490754</v>
       </c>
     </row>
     <row r="45">
@@ -48054,19 +48054,19 @@
         <v>259</v>
       </c>
       <c r="D45" t="n">
-        <v>-3.84150485927234</v>
+        <v>-3.84150485927412</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.231262034027064</v>
+        <v>-0.23126203402716</v>
       </c>
       <c r="F45" t="n">
         <v>-1.39575331653066</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.0792452834934458</v>
+        <v>-0.0792452834934423</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0000126387507762716</v>
+        <v>0.0000126387507761549</v>
       </c>
     </row>
     <row r="46">
@@ -48080,19 +48080,19 @@
         <v>259</v>
       </c>
       <c r="D46" t="n">
-        <v>-3.15396971892632</v>
+        <v>-3.15396971892703</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.31369969281606</v>
+        <v>-1.31369969281637</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.510611254860581</v>
+        <v>-0.510611254860574</v>
       </c>
       <c r="G46" t="n">
         <v>-0.217741253721066</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0467557104055368</v>
+        <v>0.0467557104054804</v>
       </c>
     </row>
     <row r="47">
@@ -48106,19 +48106,19 @@
         <v>259</v>
       </c>
       <c r="D47" t="n">
-        <v>-4.26882565599626</v>
+        <v>-4.26882565599719</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.46489501939641</v>
+        <v>-1.46489501939676</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.672076962345407</v>
+        <v>-0.672076962345404</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.236117866333725</v>
+        <v>-0.236117866333728</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0015894904688443</v>
+        <v>0.00158949046883984</v>
       </c>
     </row>
     <row r="48">
@@ -48132,10 +48132,10 @@
         <v>259</v>
       </c>
       <c r="D48" t="n">
-        <v>-2.68578081411429</v>
+        <v>-2.68578081411553</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.183011609330386</v>
+        <v>-0.18301160933047</v>
       </c>
       <c r="F48" t="n">
         <v>-1.23191605093897</v>
@@ -48144,7 +48144,7 @@
         <v>-0.0831968989405283</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0031608692075013</v>
+        <v>0.00316086920748758</v>
       </c>
     </row>
     <row r="49">
@@ -48158,19 +48158,19 @@
         <v>259</v>
       </c>
       <c r="D49" t="n">
-        <v>-3.24467607730713</v>
+        <v>-3.24467607730849</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.144636201164679</v>
+        <v>-0.144636201164716</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.978064638826453</v>
+        <v>-0.978064638826456</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.0438619030376763</v>
+        <v>-0.0438619030376692</v>
       </c>
       <c r="H49" t="n">
-        <v>0.00219067758434306</v>
+        <v>0.00219067758433339</v>
       </c>
     </row>
     <row r="50">
@@ -48184,19 +48184,19 @@
         <v>259</v>
       </c>
       <c r="D50" t="n">
-        <v>-3.22997273379714</v>
+        <v>-3.2299727337976</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.943182159431855</v>
+        <v>-0.943182159431982</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.505287898002837</v>
+        <v>-0.505287898002841</v>
       </c>
       <c r="G50" t="n">
         <v>-0.129535428773433</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0448564796196235</v>
+        <v>0.0448564796195795</v>
       </c>
     </row>
     <row r="51">
@@ -48210,10 +48210,10 @@
         <v>259</v>
       </c>
       <c r="D51" t="n">
-        <v>-2.67190643082244</v>
+        <v>-2.67190643082365</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.886071545388409</v>
+        <v>-0.886071545388813</v>
       </c>
       <c r="F51" t="n">
         <v>-1.21783807576186</v>
@@ -48222,7 +48222,7 @@
         <v>-0.407190382025334</v>
       </c>
       <c r="H51" t="n">
-        <v>0.00351463833623888</v>
+        <v>0.00351463833622416</v>
       </c>
     </row>
     <row r="52">
@@ -48236,19 +48236,19 @@
         <v>259</v>
       </c>
       <c r="D52" t="n">
-        <v>-3.78924739589303</v>
+        <v>-3.78924739589343</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.42500333790596</v>
+        <v>-1.42500333790613</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.503953360350305</v>
+        <v>-0.503953360350298</v>
       </c>
       <c r="G52" t="n">
         <v>-0.194028275245717</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0179725826286506</v>
+        <v>0.0179725826286336</v>
       </c>
     </row>
     <row r="53">
@@ -48262,19 +48262,19 @@
         <v>259</v>
       </c>
       <c r="D53" t="n">
-        <v>-3.09094752088168</v>
+        <v>-3.09094752088262</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.163094106847913</v>
+        <v>-0.163094106847961</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.573757075729741</v>
+        <v>-0.573757075729748</v>
       </c>
       <c r="G53" t="n">
         <v>-0.0304571277336123</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0357153375122715</v>
+        <v>0.0357153375122063</v>
       </c>
     </row>
     <row r="54">
@@ -48288,19 +48288,19 @@
         <v>259</v>
       </c>
       <c r="D54" t="n">
-        <v>-3.91237338553882</v>
+        <v>-3.9123733855384</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.71750211444623</v>
+        <v>-1.71750211444611</v>
       </c>
       <c r="F54" t="n">
         <v>-0.406606399888919</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.182743926255217</v>
+        <v>-0.182743926255224</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0331286672418942</v>
+        <v>0.033128667241903</v>
       </c>
     </row>
     <row r="55">
@@ -48314,19 +48314,19 @@
         <v>259</v>
       </c>
       <c r="D55" t="n">
-        <v>-3.39692672623579</v>
+        <v>-3.39692672623709</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.59030426633213</v>
+        <v>-1.59030426633273</v>
       </c>
       <c r="F55" t="n">
         <v>-0.832509728834967</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.380859785778231</v>
+        <v>-0.380859785778227</v>
       </c>
       <c r="H55" t="n">
-        <v>0.00376547712611003</v>
+        <v>0.00376547712609594</v>
       </c>
     </row>
     <row r="56">
@@ -48340,10 +48340,10 @@
         <v>259</v>
       </c>
       <c r="D56" t="n">
-        <v>-4.26297037137078</v>
+        <v>-4.26297037137056</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.65411306819558</v>
+        <v>-1.6541130681955</v>
       </c>
       <c r="F56" t="n">
         <v>-0.509492414867427</v>
@@ -48352,7 +48352,7 @@
         <v>-0.186065786535476</v>
       </c>
       <c r="H56" t="n">
-        <v>0.00799694562529591</v>
+        <v>0.00799694562529421</v>
       </c>
     </row>
     <row r="57">
@@ -48366,19 +48366,19 @@
         <v>259</v>
       </c>
       <c r="D57" t="n">
-        <v>-3.3483280247478</v>
+        <v>-3.34832802474912</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.808324926046547</v>
+        <v>-0.808324926046875</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.820148738822166</v>
+        <v>-0.820148738822159</v>
       </c>
       <c r="G57" t="n">
         <v>-0.157120579823616</v>
       </c>
       <c r="H57" t="n">
-        <v>0.00548192661773728</v>
+        <v>0.00548192661771637</v>
       </c>
     </row>
     <row r="58">
@@ -48392,19 +48392,19 @@
         <v>259</v>
       </c>
       <c r="D58" t="n">
-        <v>-3.45892869611788</v>
+        <v>-3.45892869611843</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.51876680868414</v>
+        <v>-1.5187668086844</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.499879707273124</v>
+        <v>-0.499879707273116</v>
       </c>
       <c r="G58" t="n">
         <v>-0.224712251857401</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0314246700815237</v>
+        <v>0.0314246700814899</v>
       </c>
     </row>
     <row r="59">
@@ -48418,19 +48418,19 @@
         <v>259</v>
       </c>
       <c r="D59" t="n">
-        <v>-2.40261840823305</v>
+        <v>-2.40261840823424</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.0965226271164994</v>
+        <v>-0.096522627116521</v>
       </c>
       <c r="F59" t="n">
         <v>-1.04328396921025</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.0393714920118633</v>
+        <v>-0.0393714920118526</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0166002691667841</v>
+        <v>0.0166002691667299</v>
       </c>
     </row>
     <row r="60">
@@ -48444,19 +48444,19 @@
         <v>259</v>
       </c>
       <c r="D60" t="n">
-        <v>-4.18249954175475</v>
+        <v>-4.18249954175594</v>
       </c>
       <c r="E60" t="n">
-        <v>-2.37026507714375</v>
+        <v>-2.37026507714442</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.769667406399485</v>
+        <v>-0.769667406399481</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.431402455948792</v>
+        <v>-0.431402455948788</v>
       </c>
       <c r="H60" t="n">
-        <v>0.000803919817794644</v>
+        <v>0.00080391981779155</v>
       </c>
     </row>
     <row r="61">
@@ -48470,19 +48470,19 @@
         <v>259</v>
       </c>
       <c r="D61" t="n">
-        <v>-3.48817220034216</v>
+        <v>-3.4881722003434</v>
       </c>
       <c r="E61" t="n">
-        <v>-3.45429041055345</v>
+        <v>-3.45429041055465</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.764142564725145</v>
+        <v>-0.764142564725148</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.739464072659466</v>
+        <v>-0.739464072659462</v>
       </c>
       <c r="H61" t="n">
-        <v>0.00480638078840438</v>
+        <v>0.00480638078838799</v>
       </c>
     </row>
     <row r="62">
@@ -48496,19 +48496,19 @@
         <v>259</v>
       </c>
       <c r="D62" t="n">
-        <v>-2.94752393140182</v>
+        <v>-2.94752393140233</v>
       </c>
       <c r="E62" t="n">
-        <v>-1.38887618543888</v>
+        <v>-1.38887618543914</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.618379203586191</v>
+        <v>-0.618379203586183</v>
       </c>
       <c r="G62" t="n">
         <v>-0.211086293953613</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0404548113818323</v>
+        <v>0.0404548113817805</v>
       </c>
     </row>
     <row r="63">
@@ -48522,19 +48522,19 @@
         <v>259</v>
       </c>
       <c r="D63" t="n">
-        <v>-4.6431006226428</v>
+        <v>-4.64310062264231</v>
       </c>
       <c r="E63" t="n">
-        <v>-2.91801758322992</v>
+        <v>-2.91801758322959</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.481424194198407</v>
+        <v>-0.481424194198411</v>
       </c>
       <c r="G63" t="n">
         <v>-0.309755822129894</v>
       </c>
       <c r="H63" t="n">
-        <v>0.00523848038285669</v>
+        <v>0.00523848038285758</v>
       </c>
     </row>
     <row r="64">
@@ -48548,19 +48548,19 @@
         <v>259</v>
       </c>
       <c r="D64" t="n">
-        <v>-3.97882582313899</v>
+        <v>-3.97882582314082</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.497255276289957</v>
+        <v>-0.497255276290176</v>
       </c>
       <c r="F64" t="n">
-        <v>-1.63376064442718</v>
+        <v>-1.63376064442719</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.215820109973226</v>
+        <v>-0.215820109973222</v>
       </c>
       <c r="H64" t="n">
-        <v>0.000000825730284683805</v>
+        <v>0.000000825730284674423</v>
       </c>
     </row>
     <row r="65">
@@ -48574,19 +48574,19 @@
         <v>259</v>
       </c>
       <c r="D65" t="n">
-        <v>-2.7397871253406</v>
+        <v>-2.7397871253415</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.0838078908868511</v>
+        <v>-0.0838078908868573</v>
       </c>
       <c r="F65" t="n">
         <v>-1.2052154780928</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.0139669416507218</v>
+        <v>-0.0139669416507182</v>
       </c>
       <c r="H65" t="n">
-        <v>0.00424129536733051</v>
+        <v>0.0042412953673142</v>
       </c>
     </row>
     <row r="66">
@@ -48600,19 +48600,19 @@
         <v>259</v>
       </c>
       <c r="D66" t="n">
-        <v>-3.21568007779585</v>
+        <v>-3.21568007779597</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.683832813681785</v>
+        <v>-0.683832813681684</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.55044384825155</v>
+        <v>-0.550443848251557</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.0835280412238255</v>
+        <v>-0.0835280412238113</v>
       </c>
       <c r="H66" t="n">
-        <v>0.036460557376088</v>
+        <v>0.0364605573760649</v>
       </c>
     </row>
     <row r="67">
@@ -48626,19 +48626,19 @@
         <v>259</v>
       </c>
       <c r="D67" t="n">
-        <v>-2.48838225519004</v>
+        <v>-2.4883822551913</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.6566230298969</v>
+        <v>-1.65662302989773</v>
       </c>
       <c r="F67" t="n">
         <v>-0.872094530065615</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.32344458533759</v>
+        <v>-0.323444585337588</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0304101290084785</v>
+        <v>0.0304101290083847</v>
       </c>
     </row>
     <row r="68">
@@ -48652,19 +48652,19 @@
         <v>259</v>
       </c>
       <c r="D68" t="n">
-        <v>-5.12703728883545</v>
+        <v>-5.12703728883946</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.223462003907696</v>
+        <v>-0.223462003907872</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.46202803360083</v>
+        <v>-1.46202803360082</v>
       </c>
       <c r="G68" t="n">
         <v>-0.0874957989629053</v>
       </c>
       <c r="H68" t="n">
-        <v>0.000000205646703736256</v>
+        <v>0.000000205646703731138</v>
       </c>
     </row>
     <row r="69">
@@ -48678,19 +48678,19 @@
         <v>259</v>
       </c>
       <c r="D69" t="n">
-        <v>-4.08253311744726</v>
+        <v>-4.08253311744529</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.403633371872945</v>
+        <v>-0.403633371872799</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.382516877167408</v>
+        <v>-0.382516877167401</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.0348060439418383</v>
+        <v>-0.0348060439418418</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0338156020867212</v>
+        <v>0.033815602086794</v>
       </c>
     </row>
     <row r="70">
@@ -48704,19 +48704,19 @@
         <v>259</v>
       </c>
       <c r="D70" t="n">
-        <v>-2.91392784946407</v>
+        <v>-2.91392784946499</v>
       </c>
       <c r="E70" t="n">
-        <v>-2.46744007167948</v>
+        <v>-2.46744007168027</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.608293578130187</v>
+        <v>-0.60829357813018</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.441667173414015</v>
+        <v>-0.441667173414011</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0423994348401228</v>
+        <v>0.0423994348400474</v>
       </c>
     </row>
     <row r="71">
@@ -48730,10 +48730,10 @@
         <v>259</v>
       </c>
       <c r="D71" t="n">
-        <v>-2.39450083427892</v>
+        <v>-2.39450083428028</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.4321509133169</v>
+        <v>-1.43215091331771</v>
       </c>
       <c r="F71" t="n">
         <v>-0.811168769164617</v>
@@ -48742,7 +48742,7 @@
         <v>-0.300993227490341</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0478252885606571</v>
+        <v>0.0478252885605125</v>
       </c>
     </row>
   </sheetData>

--- a/04_Figures/F04/c_data/F04_supplementary.xlsx
+++ b/04_Figures/F04/c_data/F04_supplementary.xlsx
@@ -46096,7 +46096,7 @@
         <v>3.3</v>
       </c>
       <c r="E2" t="n">
-        <v>4.82</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="3">
@@ -46110,10 +46110,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>4.82</v>
+        <v>4.1</v>
       </c>
       <c r="E3" t="n">
-        <v>5.96</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="4">
@@ -46127,10 +46127,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.96</v>
+        <v>4.7</v>
       </c>
       <c r="E4" t="n">
-        <v>6.34</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="5">
@@ -46147,7 +46147,7 @@
         <v>3.3</v>
       </c>
       <c r="E5" t="n">
-        <v>4.82</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="6">
@@ -46161,10 +46161,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>4.82</v>
+        <v>4.1</v>
       </c>
       <c r="E6" t="n">
-        <v>5.58</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
@@ -46178,10 +46178,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>5.58</v>
+        <v>4.5</v>
       </c>
       <c r="E7" t="n">
-        <v>5.96</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="8">
@@ -46198,7 +46198,7 @@
         <v>3.3</v>
       </c>
       <c r="E8" t="n">
-        <v>4.06</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="9">
@@ -46212,10 +46212,10 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>4.06</v>
+        <v>3.7</v>
       </c>
       <c r="E9" t="n">
-        <v>4.82</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="10">
@@ -46229,10 +46229,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>4.82</v>
+        <v>4.1</v>
       </c>
       <c r="E10" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="11">
@@ -46249,7 +46249,7 @@
         <v>3.3</v>
       </c>
       <c r="E11" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="12">
@@ -46263,10 +46263,10 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="E12" t="n">
-        <v>5.96</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="13">
@@ -46280,10 +46280,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.96</v>
+        <v>4.7</v>
       </c>
       <c r="E13" t="n">
-        <v>6.34</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="14">
@@ -46300,7 +46300,7 @@
         <v>3.3</v>
       </c>
       <c r="E14" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="15">
@@ -46314,10 +46314,10 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="E15" t="n">
-        <v>6.34</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="16">
@@ -46331,10 +46331,10 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>6.34</v>
+        <v>4.9</v>
       </c>
       <c r="E16" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="17">
@@ -46351,7 +46351,7 @@
         <v>3.3</v>
       </c>
       <c r="E17" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="18">
@@ -46365,10 +46365,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="E18" t="n">
-        <v>4.06</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="19">
@@ -46382,10 +46382,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.06</v>
+        <v>3.7</v>
       </c>
       <c r="E19" t="n">
-        <v>4.44</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="20">
@@ -46402,7 +46402,7 @@
         <v>3.3</v>
       </c>
       <c r="E20" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="21">
@@ -46416,10 +46416,10 @@
         <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="E21" t="n">
-        <v>6.34</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="22">
@@ -46433,10 +46433,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>6.34</v>
+        <v>4.9</v>
       </c>
       <c r="E22" t="n">
-        <v>6.72</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="23">
@@ -46453,7 +46453,7 @@
         <v>3.3</v>
       </c>
       <c r="E23" t="n">
-        <v>4.44</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="24">
@@ -46467,10 +46467,10 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>4.44</v>
+        <v>3.9</v>
       </c>
       <c r="E24" t="n">
-        <v>5.58</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="25">
@@ -46484,10 +46484,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.58</v>
+        <v>4.5</v>
       </c>
       <c r="E25" t="n">
-        <v>5.96</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="26">
@@ -46504,7 +46504,7 @@
         <v>3.3</v>
       </c>
       <c r="E26" t="n">
-        <v>4.06</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="27">
@@ -46518,10 +46518,10 @@
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>4.06</v>
+        <v>3.7</v>
       </c>
       <c r="E27" t="n">
-        <v>4.82</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="28">
@@ -46535,10 +46535,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>4.82</v>
+        <v>4.1</v>
       </c>
       <c r="E28" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="29">
@@ -46555,7 +46555,7 @@
         <v>3.3</v>
       </c>
       <c r="E29" t="n">
-        <v>4.06</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="30">
@@ -46569,10 +46569,10 @@
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>4.06</v>
+        <v>3.7</v>
       </c>
       <c r="E30" t="n">
-        <v>4.82</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="31">
@@ -46586,10 +46586,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>4.82</v>
+        <v>4.1</v>
       </c>
       <c r="E31" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="32">
@@ -46606,7 +46606,7 @@
         <v>3.3</v>
       </c>
       <c r="E32" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="33">
@@ -46620,10 +46620,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="E33" t="n">
-        <v>4.06</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="34">
@@ -46640,7 +46640,7 @@
         <v>3.3</v>
       </c>
       <c r="E34" t="n">
-        <v>5.96</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="35">
@@ -46654,10 +46654,10 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>5.96</v>
+        <v>4.7</v>
       </c>
       <c r="E35" t="n">
-        <v>7.48</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="36">
@@ -46674,7 +46674,7 @@
         <v>3.3</v>
       </c>
       <c r="E36" t="n">
-        <v>5.58</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="37">
@@ -46688,10 +46688,10 @@
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>5.58</v>
+        <v>4.5</v>
       </c>
       <c r="E37" t="n">
-        <v>6.34</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="38">
@@ -46708,7 +46708,7 @@
         <v>3.3</v>
       </c>
       <c r="E38" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="39">
@@ -46722,10 +46722,10 @@
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="E39" t="n">
-        <v>5.96</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="40">
@@ -46742,7 +46742,7 @@
         <v>3.3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="41">
@@ -46756,10 +46756,10 @@
         <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="E41" t="n">
-        <v>6.72</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="42">
@@ -46773,10 +46773,10 @@
         <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>6.72</v>
+        <v>5.1</v>
       </c>
       <c r="E42" t="n">
-        <v>8.24</v>
+        <v>5.9</v>
       </c>
     </row>
   </sheetData>

--- a/04_Figures/F04/c_data/F04_supplementary.xlsx
+++ b/04_Figures/F04/c_data/F04_supplementary.xlsx
@@ -46096,7 +46096,7 @@
         <v>3.3</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="3">
@@ -46110,10 +46110,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1</v>
+        <v>5.14</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="4">
@@ -46127,10 +46127,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7</v>
+        <v>6.52</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="5">
@@ -46147,7 +46147,7 @@
         <v>3.3</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="6">
@@ -46161,10 +46161,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>4.1</v>
+        <v>5.14</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="7">
@@ -46178,10 +46178,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.5</v>
+        <v>6.06</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="8">
@@ -46198,7 +46198,7 @@
         <v>3.3</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="9">
@@ -46212,10 +46212,10 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3.7</v>
+        <v>4.22</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="10">
@@ -46229,10 +46229,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>4.1</v>
+        <v>5.14</v>
       </c>
       <c r="E10" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="11">
@@ -46249,7 +46249,7 @@
         <v>3.3</v>
       </c>
       <c r="E11" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="12">
@@ -46263,10 +46263,10 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="E12" t="n">
-        <v>4.7</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="13">
@@ -46280,10 +46280,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7</v>
+        <v>6.52</v>
       </c>
       <c r="E13" t="n">
-        <v>4.9</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="14">
@@ -46300,7 +46300,7 @@
         <v>3.3</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="15">
@@ -46314,10 +46314,10 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="16">
@@ -46331,10 +46331,10 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>4.9</v>
+        <v>6.98</v>
       </c>
       <c r="E16" t="n">
-        <v>5.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="17">
@@ -46351,7 +46351,7 @@
         <v>3.3</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="18">
@@ -46365,10 +46365,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="E18" t="n">
-        <v>3.7</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="19">
@@ -46382,10 +46382,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.7</v>
+        <v>4.22</v>
       </c>
       <c r="E19" t="n">
-        <v>3.9</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="20">
@@ -46402,7 +46402,7 @@
         <v>3.3</v>
       </c>
       <c r="E20" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="21">
@@ -46416,10 +46416,10 @@
         <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="E21" t="n">
-        <v>4.9</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="22">
@@ -46433,10 +46433,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>4.9</v>
+        <v>6.98</v>
       </c>
       <c r="E22" t="n">
-        <v>5.1</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="23">
@@ -46453,7 +46453,7 @@
         <v>3.3</v>
       </c>
       <c r="E23" t="n">
-        <v>3.9</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="24">
@@ -46467,10 +46467,10 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>3.9</v>
+        <v>4.68</v>
       </c>
       <c r="E24" t="n">
-        <v>4.5</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="25">
@@ -46484,10 +46484,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.5</v>
+        <v>6.06</v>
       </c>
       <c r="E25" t="n">
-        <v>4.7</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="26">
@@ -46504,7 +46504,7 @@
         <v>3.3</v>
       </c>
       <c r="E26" t="n">
-        <v>3.7</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="27">
@@ -46518,10 +46518,10 @@
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>3.7</v>
+        <v>4.22</v>
       </c>
       <c r="E27" t="n">
-        <v>4.1</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="28">
@@ -46535,10 +46535,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>4.1</v>
+        <v>5.14</v>
       </c>
       <c r="E28" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="29">
@@ -46555,7 +46555,7 @@
         <v>3.3</v>
       </c>
       <c r="E29" t="n">
-        <v>3.7</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="30">
@@ -46569,10 +46569,10 @@
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>3.7</v>
+        <v>4.22</v>
       </c>
       <c r="E30" t="n">
-        <v>4.1</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="31">
@@ -46586,10 +46586,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>4.1</v>
+        <v>5.14</v>
       </c>
       <c r="E31" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="32">
@@ -46606,7 +46606,7 @@
         <v>3.3</v>
       </c>
       <c r="E32" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="33">
@@ -46620,10 +46620,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="E33" t="n">
-        <v>3.7</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="34">
@@ -46640,7 +46640,7 @@
         <v>3.3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.7</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="35">
@@ -46654,10 +46654,10 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>4.7</v>
+        <v>6.52</v>
       </c>
       <c r="E35" t="n">
-        <v>5.5</v>
+        <v>8.36</v>
       </c>
     </row>
     <row r="36">
@@ -46674,7 +46674,7 @@
         <v>3.3</v>
       </c>
       <c r="E36" t="n">
-        <v>4.5</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="37">
@@ -46688,10 +46688,10 @@
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>4.5</v>
+        <v>6.06</v>
       </c>
       <c r="E37" t="n">
-        <v>4.9</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="38">
@@ -46708,7 +46708,7 @@
         <v>3.3</v>
       </c>
       <c r="E38" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="39">
@@ -46722,10 +46722,10 @@
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="E39" t="n">
-        <v>4.7</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="40">
@@ -46742,7 +46742,7 @@
         <v>3.3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="41">
@@ -46756,10 +46756,10 @@
         <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="E41" t="n">
-        <v>5.1</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="42">
@@ -46773,10 +46773,10 @@
         <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>5.1</v>
+        <v>7.44</v>
       </c>
       <c r="E42" t="n">
-        <v>5.9</v>
+        <v>9.28</v>
       </c>
     </row>
   </sheetData>

--- a/04_Figures/F04/c_data/F04_supplementary.xlsx
+++ b/04_Figures/F04/c_data/F04_supplementary.xlsx
@@ -36258,25 +36258,25 @@
         <v>218</v>
       </c>
       <c r="D2" t="n">
-        <v>3.48412721247129</v>
+        <v>3.48412721247115</v>
       </c>
       <c r="E2" t="n">
-        <v>4.21161096897919</v>
+        <v>4.21161096897894</v>
       </c>
       <c r="F2" t="n">
         <v>0.511141040596115</v>
       </c>
       <c r="G2" t="n">
-        <v>0.556196949731639</v>
+        <v>0.556196949731628</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0287632004854532</v>
+        <v>0.0287632004854626</v>
       </c>
       <c r="I2" t="s">
         <v>219</v>
       </c>
       <c r="J2" t="n">
-        <v>4.21161096897919</v>
+        <v>4.21161096897894</v>
       </c>
       <c r="K2" t="s">
         <v>15</v>
@@ -36293,25 +36293,25 @@
         <v>218</v>
       </c>
       <c r="D3" t="n">
-        <v>4.05790561093415</v>
+        <v>4.05790561093385</v>
       </c>
       <c r="E3" t="n">
-        <v>4.09186896159768</v>
+        <v>4.09186896159723</v>
       </c>
       <c r="F3" t="n">
-        <v>0.706915668807518</v>
+        <v>0.706915668807515</v>
       </c>
       <c r="G3" t="n">
-        <v>0.64771515727271</v>
+        <v>0.647715157272685</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00213423371891747</v>
+        <v>0.00213423371891966</v>
       </c>
       <c r="I3" t="s">
         <v>219</v>
       </c>
       <c r="J3" t="n">
-        <v>4.09186896159768</v>
+        <v>4.09186896159723</v>
       </c>
       <c r="K3" t="s">
         <v>15</v>
@@ -36328,25 +36328,25 @@
         <v>220</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.4881722003434</v>
+        <v>-3.48817220034292</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.45429041055465</v>
+        <v>-3.45429041055405</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.764142564725148</v>
+        <v>-0.764142564725137</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.739464072659462</v>
+        <v>-0.739464072659423</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00480638078838799</v>
+        <v>0.00480638078839455</v>
       </c>
       <c r="I4" t="s">
         <v>221</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45429041055465</v>
+        <v>3.45429041055405</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
@@ -36363,25 +36363,25 @@
         <v>218</v>
       </c>
       <c r="D5" t="n">
-        <v>2.59704840828289</v>
+        <v>2.5970484082824</v>
       </c>
       <c r="E5" t="n">
-        <v>3.43072370614807</v>
+        <v>3.43072370614742</v>
       </c>
       <c r="F5" t="n">
         <v>1.10652955402938</v>
       </c>
       <c r="G5" t="n">
-        <v>1.71883830144357</v>
+        <v>1.71883830144356</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00758883678460189</v>
+        <v>0.00758883678461347</v>
       </c>
       <c r="I5" t="s">
         <v>219</v>
       </c>
       <c r="J5" t="n">
-        <v>3.43072370614807</v>
+        <v>3.43072370614742</v>
       </c>
       <c r="K5" t="s">
         <v>15</v>
@@ -36398,25 +36398,25 @@
         <v>220</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.64310062264231</v>
+        <v>-4.6431006226425</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.91801758322959</v>
+        <v>-2.91801758322966</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.481424194198411</v>
+        <v>-0.481424194198414</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.309755822129894</v>
+        <v>-0.30975582212989</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00523848038285758</v>
+        <v>0.00523848038285679</v>
       </c>
       <c r="I6" t="s">
         <v>221</v>
       </c>
       <c r="J6" t="n">
-        <v>2.91801758322959</v>
+        <v>2.91801758322966</v>
       </c>
       <c r="K6" t="s">
         <v>39</v>
@@ -36433,25 +36433,25 @@
         <v>218</v>
       </c>
       <c r="D7" t="n">
-        <v>3.76368067195992</v>
+        <v>3.76368067196001</v>
       </c>
       <c r="E7" t="n">
-        <v>2.88994882485869</v>
+        <v>2.88994882485905</v>
       </c>
       <c r="F7" t="n">
-        <v>0.390491085452172</v>
+        <v>0.390491085452169</v>
       </c>
       <c r="G7" t="n">
-        <v>0.306973060642743</v>
+        <v>0.306973060642772</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0458883291390259</v>
+        <v>0.045888329139026</v>
       </c>
       <c r="I7" t="s">
         <v>219</v>
       </c>
       <c r="J7" t="n">
-        <v>2.88994882485869</v>
+        <v>2.88994882485905</v>
       </c>
       <c r="K7" t="s">
         <v>15</v>
@@ -36468,25 +36468,25 @@
         <v>218</v>
       </c>
       <c r="D8" t="n">
-        <v>4.6362501064832</v>
+        <v>4.63625010648391</v>
       </c>
       <c r="E8" t="n">
-        <v>2.88766399959219</v>
+        <v>2.88766399959269</v>
       </c>
       <c r="F8" t="n">
-        <v>0.433831594366477</v>
+        <v>0.433831594366481</v>
       </c>
       <c r="G8" t="n">
-        <v>0.25369598668917</v>
+        <v>0.253695986689177</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00936752333385777</v>
+        <v>0.00936752333384944</v>
       </c>
       <c r="I8" t="s">
         <v>219</v>
       </c>
       <c r="J8" t="n">
-        <v>2.88766399959219</v>
+        <v>2.88766399959269</v>
       </c>
       <c r="K8" t="s">
         <v>15</v>
@@ -36503,25 +36503,25 @@
         <v>218</v>
       </c>
       <c r="D9" t="n">
-        <v>5.39120431822591</v>
+        <v>5.39120431822665</v>
       </c>
       <c r="E9" t="n">
-        <v>2.75946428310965</v>
+        <v>2.75946428311011</v>
       </c>
       <c r="F9" t="n">
-        <v>0.473425956401492</v>
+        <v>0.473425956401499</v>
       </c>
       <c r="G9" t="n">
-        <v>0.248086314903833</v>
+        <v>0.248086314903844</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00154451475019621</v>
+        <v>0.00154451475019456</v>
       </c>
       <c r="I9" t="s">
         <v>219</v>
       </c>
       <c r="J9" t="n">
-        <v>2.75946428310965</v>
+        <v>2.75946428311011</v>
       </c>
       <c r="K9" t="s">
         <v>15</v>
@@ -36538,25 +36538,25 @@
         <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.20564732472382</v>
+        <v>-3.20564732472344</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.70712786773453</v>
+        <v>-2.70712786773419</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.814653105627787</v>
+        <v>-0.814653105627801</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.693627278270892</v>
+        <v>-0.693627278270899</v>
       </c>
       <c r="H10" t="n">
-        <v>0.006699503612022</v>
+        <v>0.00669950361202838</v>
       </c>
       <c r="I10" t="s">
         <v>221</v>
       </c>
       <c r="J10" t="n">
-        <v>2.70712786773453</v>
+        <v>2.70712786773419</v>
       </c>
       <c r="K10" t="s">
         <v>39</v>
@@ -36573,25 +36573,25 @@
         <v>218</v>
       </c>
       <c r="D11" t="n">
-        <v>4.62111071584404</v>
+        <v>4.62111071584342</v>
       </c>
       <c r="E11" t="n">
-        <v>2.67928195405153</v>
+        <v>2.67928195405119</v>
       </c>
       <c r="F11" t="n">
-        <v>1.11357792651978</v>
+        <v>1.11357792651977</v>
       </c>
       <c r="G11" t="n">
-        <v>0.661004499617036</v>
+        <v>0.66100449961704</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00000578698121710783</v>
+        <v>0.00000578698121712521</v>
       </c>
       <c r="I11" t="s">
         <v>219</v>
       </c>
       <c r="J11" t="n">
-        <v>2.67928195405153</v>
+        <v>2.67928195405119</v>
       </c>
       <c r="K11" t="s">
         <v>15</v>
@@ -36608,25 +36608,25 @@
         <v>220</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.91392784946499</v>
+        <v>-2.91392784946468</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.46744007168027</v>
+        <v>-2.46744007167997</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.60829357813018</v>
+        <v>-0.608293578130183</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.441667173414011</v>
+        <v>-0.441667173414007</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0423994348400474</v>
+        <v>0.0423994348400729</v>
       </c>
       <c r="I12" t="s">
         <v>221</v>
       </c>
       <c r="J12" t="n">
-        <v>2.46744007168027</v>
+        <v>2.46744007167997</v>
       </c>
       <c r="K12" t="s">
         <v>39</v>
@@ -36643,25 +36643,25 @@
         <v>218</v>
       </c>
       <c r="D13" t="n">
-        <v>3.56494917113622</v>
+        <v>3.56494917113591</v>
       </c>
       <c r="E13" t="n">
-        <v>2.43367358253536</v>
+        <v>2.4336735825353</v>
       </c>
       <c r="F13" t="n">
-        <v>0.538929847075678</v>
+        <v>0.538929847075671</v>
       </c>
       <c r="G13" t="n">
-        <v>0.376663015654117</v>
+        <v>0.376663015654135</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0200502138750984</v>
+        <v>0.0200502138751121</v>
       </c>
       <c r="I13" t="s">
         <v>219</v>
       </c>
       <c r="J13" t="n">
-        <v>2.43367358253536</v>
+        <v>2.4336735825353</v>
       </c>
       <c r="K13" t="s">
         <v>15</v>
@@ -36678,25 +36678,25 @@
         <v>220</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.18249954175594</v>
+        <v>-4.18249954175544</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.37026507714442</v>
+        <v>-2.37026507714425</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.769667406399481</v>
+        <v>-0.769667406399471</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.431402455948788</v>
+        <v>-0.431402455948803</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00080391981779155</v>
+        <v>0.00080391981779289</v>
       </c>
       <c r="I14" t="s">
         <v>221</v>
       </c>
       <c r="J14" t="n">
-        <v>2.37026507714442</v>
+        <v>2.37026507714425</v>
       </c>
       <c r="K14" t="s">
         <v>39</v>
@@ -36713,25 +36713,25 @@
         <v>218</v>
       </c>
       <c r="D15" t="n">
-        <v>3.25356019722925</v>
+        <v>3.25356019722879</v>
       </c>
       <c r="E15" t="n">
-        <v>2.32286999909631</v>
+        <v>2.32286999909601</v>
       </c>
       <c r="F15" t="n">
-        <v>0.900404254930407</v>
+        <v>0.900404254930406</v>
       </c>
       <c r="G15" t="n">
-        <v>0.413709003406987</v>
+        <v>0.413709003406991</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00466372750746012</v>
+        <v>0.00466372750746704</v>
       </c>
       <c r="I15" t="s">
         <v>219</v>
       </c>
       <c r="J15" t="n">
-        <v>2.32286999909631</v>
+        <v>2.32286999909601</v>
       </c>
       <c r="K15" t="s">
         <v>15</v>
@@ -36748,25 +36748,25 @@
         <v>218</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0178573046977</v>
+        <v>4.01785730469785</v>
       </c>
       <c r="E16" t="n">
-        <v>2.29300875076201</v>
+        <v>2.2930087507622</v>
       </c>
       <c r="F16" t="n">
-        <v>0.402624473620968</v>
+        <v>0.402624473620961</v>
       </c>
       <c r="G16" t="n">
-        <v>0.235246478227104</v>
+        <v>0.235246478227111</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0297225836246233</v>
+        <v>0.0297225836246227</v>
       </c>
       <c r="I16" t="s">
         <v>219</v>
       </c>
       <c r="J16" t="n">
-        <v>2.29300875076201</v>
+        <v>2.2930087507622</v>
       </c>
       <c r="K16" t="s">
         <v>15</v>
@@ -36783,25 +36783,25 @@
         <v>218</v>
       </c>
       <c r="D17" t="n">
-        <v>3.98464356645387</v>
+        <v>3.9846435664542</v>
       </c>
       <c r="E17" t="n">
-        <v>2.25856204382237</v>
+        <v>2.2585620438228</v>
       </c>
       <c r="F17" t="n">
-        <v>0.349460320731534</v>
+        <v>0.34946032073152</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2027926331901</v>
+        <v>0.202792633190114</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0491609257512415</v>
+        <v>0.049160925751234</v>
       </c>
       <c r="I17" t="s">
         <v>219</v>
       </c>
       <c r="J17" t="n">
-        <v>2.25856204382237</v>
+        <v>2.2585620438228</v>
       </c>
       <c r="K17" t="s">
         <v>15</v>
@@ -36818,25 +36818,25 @@
         <v>218</v>
       </c>
       <c r="D18" t="n">
-        <v>3.73354463132545</v>
+        <v>3.73354463132493</v>
       </c>
       <c r="E18" t="n">
-        <v>2.13914502585476</v>
+        <v>2.13914502585422</v>
       </c>
       <c r="F18" t="n">
-        <v>0.776205944356491</v>
+        <v>0.776205944356487</v>
       </c>
       <c r="G18" t="n">
-        <v>0.452181538535665</v>
+        <v>0.452181538535612</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0025772311745655</v>
+        <v>0.00257723117456945</v>
       </c>
       <c r="I18" t="s">
         <v>219</v>
       </c>
       <c r="J18" t="n">
-        <v>2.13914502585476</v>
+        <v>2.13914502585422</v>
       </c>
       <c r="K18" t="s">
         <v>15</v>
@@ -36853,25 +36853,25 @@
         <v>218</v>
       </c>
       <c r="D19" t="n">
-        <v>3.9078914232885</v>
+        <v>3.90789142328831</v>
       </c>
       <c r="E19" t="n">
-        <v>2.02585547110802</v>
+        <v>2.02585547110797</v>
       </c>
       <c r="F19" t="n">
-        <v>0.611262057913596</v>
+        <v>0.611262057913599</v>
       </c>
       <c r="G19" t="n">
-        <v>0.285039023149757</v>
+        <v>0.285039023149764</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00639334703822732</v>
+        <v>0.00639334703823077</v>
       </c>
       <c r="I19" t="s">
         <v>219</v>
       </c>
       <c r="J19" t="n">
-        <v>2.02585547110802</v>
+        <v>2.02585547110797</v>
       </c>
       <c r="K19" t="s">
         <v>15</v>
@@ -36888,25 +36888,25 @@
         <v>218</v>
       </c>
       <c r="D20" t="n">
-        <v>4.63999909161819</v>
+        <v>4.63999909161752</v>
       </c>
       <c r="E20" t="n">
-        <v>1.95027028471445</v>
+        <v>1.95027028471429</v>
       </c>
       <c r="F20" t="n">
-        <v>1.01770635395492</v>
+        <v>1.0177063539549</v>
       </c>
       <c r="G20" t="n">
-        <v>0.437936508011408</v>
+        <v>0.437936508011425</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0000152558240329967</v>
+        <v>0.0000152558240330445</v>
       </c>
       <c r="I20" t="s">
         <v>219</v>
       </c>
       <c r="J20" t="n">
-        <v>1.95027028471445</v>
+        <v>1.95027028471429</v>
       </c>
       <c r="K20" t="s">
         <v>15</v>
@@ -36923,25 +36923,25 @@
         <v>218</v>
       </c>
       <c r="D21" t="n">
-        <v>4.98144460589381</v>
+        <v>4.98144460589374</v>
       </c>
       <c r="E21" t="n">
-        <v>1.94065606360796</v>
+        <v>1.94065606360806</v>
       </c>
       <c r="F21" t="n">
-        <v>0.540644965102565</v>
+        <v>0.540644965102548</v>
       </c>
       <c r="G21" t="n">
-        <v>0.21563397466149</v>
+        <v>0.215633974661497</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00141070927441336</v>
+        <v>0.00141070927441428</v>
       </c>
       <c r="I21" t="s">
         <v>219</v>
       </c>
       <c r="J21" t="n">
-        <v>1.94065606360796</v>
+        <v>1.94065606360806</v>
       </c>
       <c r="K21" t="s">
         <v>15</v>
